--- a/AAII_Financials/Yearly/ATHM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ATHM_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>958400</v>
+        <v>998700</v>
       </c>
       <c r="E8" s="3">
-        <v>999300</v>
+        <v>964900</v>
       </c>
       <c r="F8" s="3">
-        <v>1195600</v>
+        <v>1006100</v>
       </c>
       <c r="G8" s="3">
-        <v>1162700</v>
+        <v>1203700</v>
       </c>
       <c r="H8" s="3">
-        <v>998800</v>
+        <v>1170700</v>
       </c>
       <c r="I8" s="3">
-        <v>857500</v>
+        <v>1005600</v>
       </c>
       <c r="J8" s="3">
+        <v>863300</v>
+      </c>
+      <c r="K8" s="3">
         <v>823200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>482200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>333900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>185100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>105100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>63000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>157100</v>
+        <v>196300</v>
       </c>
       <c r="E9" s="3">
-        <v>139300</v>
+        <v>158200</v>
       </c>
       <c r="F9" s="3">
-        <v>119300</v>
+        <v>140200</v>
       </c>
       <c r="G9" s="3">
-        <v>106400</v>
+        <v>120100</v>
       </c>
       <c r="H9" s="3">
-        <v>81200</v>
+        <v>107100</v>
       </c>
       <c r="I9" s="3">
-        <v>120700</v>
+        <v>81800</v>
       </c>
       <c r="J9" s="3">
+        <v>121500</v>
+      </c>
+      <c r="K9" s="3">
         <v>282200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>52900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>29800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>21800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>25600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>801300</v>
+        <v>802500</v>
       </c>
       <c r="E10" s="3">
-        <v>860000</v>
+        <v>806700</v>
       </c>
       <c r="F10" s="3">
-        <v>1076200</v>
+        <v>865900</v>
       </c>
       <c r="G10" s="3">
-        <v>1056400</v>
+        <v>1083600</v>
       </c>
       <c r="H10" s="3">
-        <v>917500</v>
+        <v>1063600</v>
       </c>
       <c r="I10" s="3">
-        <v>736800</v>
+        <v>923800</v>
       </c>
       <c r="J10" s="3">
+        <v>741900</v>
+      </c>
+      <c r="K10" s="3">
         <v>541000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>429300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>304100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>163200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>79500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>44000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>195700</v>
+        <v>187500</v>
       </c>
       <c r="E12" s="3">
-        <v>193000</v>
+        <v>197000</v>
       </c>
       <c r="F12" s="3">
-        <v>188400</v>
+        <v>194400</v>
       </c>
       <c r="G12" s="3">
-        <v>178300</v>
+        <v>189700</v>
       </c>
       <c r="H12" s="3">
-        <v>156800</v>
+        <v>179500</v>
       </c>
       <c r="I12" s="3">
-        <v>121300</v>
+        <v>157800</v>
       </c>
       <c r="J12" s="3">
+        <v>122200</v>
+      </c>
+      <c r="K12" s="3">
         <v>78900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>38100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2400</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -944,20 +960,23 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="3">
         <v>-7800</v>
       </c>
-      <c r="E14" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>17</v>
+      <c r="F14" s="3">
+        <v>-7200</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>17</v>
@@ -974,8 +993,8 @@
       <c r="K14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -986,9 +1005,12 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>823600</v>
+        <v>877300</v>
       </c>
       <c r="E17" s="3">
-        <v>786800</v>
+        <v>829200</v>
       </c>
       <c r="F17" s="3">
-        <v>822100</v>
+        <v>792100</v>
       </c>
       <c r="G17" s="3">
-        <v>781900</v>
+        <v>827700</v>
       </c>
       <c r="H17" s="3">
-        <v>649800</v>
+        <v>787200</v>
       </c>
       <c r="I17" s="3">
-        <v>575400</v>
+        <v>654200</v>
       </c>
       <c r="J17" s="3">
+        <v>579300</v>
+      </c>
+      <c r="K17" s="3">
         <v>663900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>315200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>192400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>100600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>62300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>38000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>134800</v>
+        <v>121400</v>
       </c>
       <c r="E18" s="3">
-        <v>212500</v>
+        <v>135700</v>
       </c>
       <c r="F18" s="3">
-        <v>373500</v>
+        <v>214000</v>
       </c>
       <c r="G18" s="3">
-        <v>380800</v>
+        <v>376000</v>
       </c>
       <c r="H18" s="3">
-        <v>349000</v>
+        <v>383400</v>
       </c>
       <c r="I18" s="3">
-        <v>282100</v>
+        <v>351400</v>
       </c>
       <c r="J18" s="3">
+        <v>284100</v>
+      </c>
+      <c r="K18" s="3">
         <v>159300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>167000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>141600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>84400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>42800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>25000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1146,92 +1178,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>108600</v>
+        <v>156300</v>
       </c>
       <c r="E20" s="3">
-        <v>88100</v>
+        <v>109300</v>
       </c>
       <c r="F20" s="3">
-        <v>133100</v>
+        <v>88700</v>
       </c>
       <c r="G20" s="3">
-        <v>130200</v>
+        <v>134000</v>
       </c>
       <c r="H20" s="3">
-        <v>98600</v>
+        <v>131100</v>
       </c>
       <c r="I20" s="3">
-        <v>30100</v>
+        <v>99200</v>
       </c>
       <c r="J20" s="3">
+        <v>30300</v>
+      </c>
+      <c r="K20" s="3">
         <v>13200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>10600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3">
-        <v>285500</v>
+      <c r="D21" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E21" s="3">
-        <v>343300</v>
+        <v>287500</v>
       </c>
       <c r="F21" s="3">
-        <v>530000</v>
+        <v>345700</v>
       </c>
       <c r="G21" s="3">
-        <v>527400</v>
+        <v>533700</v>
       </c>
       <c r="H21" s="3">
-        <v>461600</v>
+        <v>531000</v>
       </c>
       <c r="I21" s="3">
-        <v>324500</v>
+        <v>464800</v>
       </c>
       <c r="J21" s="3">
+        <v>326800</v>
+      </c>
+      <c r="K21" s="3">
         <v>182100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>185500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>153800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>91400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>47100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>30500</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1263,101 +1302,110 @@
         <v>0</v>
       </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>243400</v>
+        <v>277700</v>
       </c>
       <c r="E23" s="3">
-        <v>300600</v>
+        <v>245100</v>
       </c>
       <c r="F23" s="3">
-        <v>506500</v>
+        <v>302700</v>
       </c>
       <c r="G23" s="3">
-        <v>511000</v>
+        <v>510000</v>
       </c>
       <c r="H23" s="3">
-        <v>447600</v>
+        <v>514500</v>
       </c>
       <c r="I23" s="3">
-        <v>312300</v>
+        <v>450600</v>
       </c>
       <c r="J23" s="3">
+        <v>314400</v>
+      </c>
+      <c r="K23" s="3">
         <v>172400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>177600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>147400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>86500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>43600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>25300</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-8500</v>
+        <v>10000</v>
       </c>
       <c r="E24" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="F24" s="3">
         <v>4700</v>
       </c>
-      <c r="F24" s="3">
-        <v>36000</v>
-      </c>
       <c r="G24" s="3">
-        <v>69100</v>
+        <v>36300</v>
       </c>
       <c r="H24" s="3">
-        <v>52200</v>
+        <v>69600</v>
       </c>
       <c r="I24" s="3">
-        <v>36900</v>
+        <v>52500</v>
       </c>
       <c r="J24" s="3">
+        <v>37100</v>
+      </c>
+      <c r="K24" s="3">
         <v>4500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>39700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>30200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>17100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>13100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5600</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>251900</v>
+        <v>267700</v>
       </c>
       <c r="E26" s="3">
-        <v>295900</v>
+        <v>253700</v>
       </c>
       <c r="F26" s="3">
-        <v>470500</v>
+        <v>297900</v>
       </c>
       <c r="G26" s="3">
-        <v>441900</v>
+        <v>473700</v>
       </c>
       <c r="H26" s="3">
-        <v>395400</v>
+        <v>445000</v>
       </c>
       <c r="I26" s="3">
-        <v>275400</v>
+        <v>398100</v>
       </c>
       <c r="J26" s="3">
+        <v>277300</v>
+      </c>
+      <c r="K26" s="3">
         <v>167900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>137900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>117200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>69400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>30500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>19700</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>249500</v>
+        <v>261400</v>
       </c>
       <c r="E27" s="3">
-        <v>296700</v>
+        <v>251200</v>
       </c>
       <c r="F27" s="3">
-        <v>470200</v>
+        <v>298700</v>
       </c>
       <c r="G27" s="3">
-        <v>441900</v>
+        <v>473400</v>
       </c>
       <c r="H27" s="3">
-        <v>396400</v>
+        <v>444900</v>
       </c>
       <c r="I27" s="3">
-        <v>276400</v>
+        <v>399100</v>
       </c>
       <c r="J27" s="3">
+        <v>278300</v>
+      </c>
+      <c r="K27" s="3">
         <v>169600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>137900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>117200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>69400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>30500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>19700</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1563,11 +1623,14 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-600</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-108600</v>
+        <v>-156300</v>
       </c>
       <c r="E32" s="3">
-        <v>-88100</v>
+        <v>-109300</v>
       </c>
       <c r="F32" s="3">
-        <v>-133100</v>
+        <v>-88700</v>
       </c>
       <c r="G32" s="3">
-        <v>-130200</v>
+        <v>-134000</v>
       </c>
       <c r="H32" s="3">
-        <v>-98600</v>
+        <v>-131100</v>
       </c>
       <c r="I32" s="3">
-        <v>-30100</v>
+        <v>-99200</v>
       </c>
       <c r="J32" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-13200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-10600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>249500</v>
+        <v>261400</v>
       </c>
       <c r="E33" s="3">
-        <v>296700</v>
+        <v>251200</v>
       </c>
       <c r="F33" s="3">
-        <v>470200</v>
+        <v>298700</v>
       </c>
       <c r="G33" s="3">
-        <v>441900</v>
+        <v>473400</v>
       </c>
       <c r="H33" s="3">
-        <v>396400</v>
+        <v>444900</v>
       </c>
       <c r="I33" s="3">
-        <v>276400</v>
+        <v>399100</v>
       </c>
       <c r="J33" s="3">
+        <v>278300</v>
+      </c>
+      <c r="K33" s="3">
         <v>169600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>137900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>117200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>69400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>30500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>19100</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>249500</v>
+        <v>261400</v>
       </c>
       <c r="E35" s="3">
-        <v>296700</v>
+        <v>251200</v>
       </c>
       <c r="F35" s="3">
-        <v>470200</v>
+        <v>298700</v>
       </c>
       <c r="G35" s="3">
-        <v>441900</v>
+        <v>473400</v>
       </c>
       <c r="H35" s="3">
-        <v>396400</v>
+        <v>444900</v>
       </c>
       <c r="I35" s="3">
-        <v>276400</v>
+        <v>399100</v>
       </c>
       <c r="J35" s="3">
+        <v>278300</v>
+      </c>
+      <c r="K35" s="3">
         <v>169600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>137900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>117200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>69400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>30500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>19100</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,82 +1986,86 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>386800</v>
+        <v>694600</v>
       </c>
       <c r="E41" s="3">
-        <v>585000</v>
+        <v>389400</v>
       </c>
       <c r="F41" s="3">
-        <v>241800</v>
+        <v>589000</v>
       </c>
       <c r="G41" s="3">
-        <v>274500</v>
+        <v>243500</v>
       </c>
       <c r="H41" s="3">
-        <v>29300</v>
+        <v>276400</v>
       </c>
       <c r="I41" s="3">
-        <v>125900</v>
+        <v>29500</v>
       </c>
       <c r="J41" s="3">
+        <v>126700</v>
+      </c>
+      <c r="K41" s="3">
         <v>454800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>299600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>165100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>173200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>60300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>31100</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2665000</v>
+        <v>2579100</v>
       </c>
       <c r="E42" s="3">
-        <v>2280600</v>
+        <v>2683100</v>
       </c>
       <c r="F42" s="3">
-        <v>1779700</v>
+        <v>2296100</v>
       </c>
       <c r="G42" s="3">
-        <v>1494900</v>
+        <v>1791800</v>
       </c>
       <c r="H42" s="3">
-        <v>1360900</v>
+        <v>1505100</v>
       </c>
       <c r="I42" s="3">
-        <v>1001700</v>
+        <v>1370200</v>
       </c>
       <c r="J42" s="3">
+        <v>1008500</v>
+      </c>
+      <c r="K42" s="3">
         <v>335800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>273600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>269100</v>
-      </c>
-      <c r="M42" s="3">
-        <v>300</v>
       </c>
       <c r="N42" s="3">
         <v>300</v>
@@ -1984,80 +2073,86 @@
       <c r="O42" s="3">
         <v>300</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>278700</v>
+        <v>207000</v>
       </c>
       <c r="E43" s="3">
-        <v>312800</v>
+        <v>280600</v>
       </c>
       <c r="F43" s="3">
-        <v>437900</v>
+        <v>314900</v>
       </c>
       <c r="G43" s="3">
-        <v>450300</v>
+        <v>440900</v>
       </c>
       <c r="H43" s="3">
-        <v>390800</v>
+        <v>453300</v>
       </c>
       <c r="I43" s="3">
-        <v>264900</v>
+        <v>393400</v>
       </c>
       <c r="J43" s="3">
+        <v>266700</v>
+      </c>
+      <c r="K43" s="3">
         <v>342900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>156800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>119800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>71200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>46900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>30200</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>17</v>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
+        <v>0</v>
       </c>
       <c r="I44" s="3">
         <v>0</v>
       </c>
       <c r="J44" s="3">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3">
         <v>13200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>15500</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>17</v>
@@ -2068,122 +2163,131 @@
       <c r="O44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>42100</v>
+        <v>67800</v>
       </c>
       <c r="E45" s="3">
-        <v>42500</v>
+        <v>42400</v>
       </c>
       <c r="F45" s="3">
-        <v>76300</v>
+        <v>42800</v>
       </c>
       <c r="G45" s="3">
-        <v>39100</v>
+        <v>76800</v>
       </c>
       <c r="H45" s="3">
-        <v>33600</v>
+        <v>39300</v>
       </c>
       <c r="I45" s="3">
-        <v>24100</v>
+        <v>33800</v>
       </c>
       <c r="J45" s="3">
+        <v>24200</v>
+      </c>
+      <c r="K45" s="3">
         <v>111900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>53800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>44200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4100</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3372600</v>
+        <v>3548500</v>
       </c>
       <c r="E46" s="3">
-        <v>3220800</v>
+        <v>3395600</v>
       </c>
       <c r="F46" s="3">
-        <v>2535700</v>
+        <v>3242700</v>
       </c>
       <c r="G46" s="3">
-        <v>2258800</v>
+        <v>2553000</v>
       </c>
       <c r="H46" s="3">
-        <v>1814600</v>
+        <v>2274100</v>
       </c>
       <c r="I46" s="3">
-        <v>1416500</v>
+        <v>1826900</v>
       </c>
       <c r="J46" s="3">
+        <v>1426100</v>
+      </c>
+      <c r="K46" s="3">
         <v>1026300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>799400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>570000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>288900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>112800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>65700</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>59200</v>
+        <v>64600</v>
       </c>
       <c r="E47" s="3">
-        <v>10800</v>
+        <v>59600</v>
       </c>
       <c r="F47" s="3">
-        <v>12200</v>
+        <v>10900</v>
       </c>
       <c r="G47" s="3">
-        <v>10500</v>
+        <v>12300</v>
       </c>
       <c r="H47" s="3">
-        <v>10100</v>
+        <v>10600</v>
       </c>
       <c r="I47" s="3">
-        <v>21900</v>
+        <v>10200</v>
       </c>
       <c r="J47" s="3">
+        <v>22100</v>
+      </c>
+      <c r="K47" s="3">
         <v>18700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>17300</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>17</v>
@@ -2194,93 +2298,102 @@
       <c r="O47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>51100</v>
+        <v>27900</v>
       </c>
       <c r="E48" s="3">
-        <v>71100</v>
+        <v>51500</v>
       </c>
       <c r="F48" s="3">
-        <v>85500</v>
+        <v>71600</v>
       </c>
       <c r="G48" s="3">
-        <v>50100</v>
+        <v>86100</v>
       </c>
       <c r="H48" s="3">
-        <v>23500</v>
+        <v>50400</v>
       </c>
       <c r="I48" s="3">
-        <v>18000</v>
+        <v>23700</v>
       </c>
       <c r="J48" s="3">
+        <v>18100</v>
+      </c>
+      <c r="K48" s="3">
         <v>37200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>582700</v>
+        <v>576100</v>
       </c>
       <c r="E49" s="3">
-        <v>593600</v>
+        <v>586700</v>
       </c>
       <c r="F49" s="3">
-        <v>623000</v>
+        <v>597700</v>
       </c>
       <c r="G49" s="3">
-        <v>211500</v>
+        <v>627200</v>
       </c>
       <c r="H49" s="3">
-        <v>213200</v>
+        <v>213000</v>
       </c>
       <c r="I49" s="3">
-        <v>214700</v>
+        <v>214600</v>
       </c>
       <c r="J49" s="3">
+        <v>216200</v>
+      </c>
+      <c r="K49" s="3">
         <v>423600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>214100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>241700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>235700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>222900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>227400</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>37500</v>
+        <v>69700</v>
       </c>
       <c r="E52" s="3">
-        <v>25000</v>
+        <v>37700</v>
       </c>
       <c r="F52" s="3">
-        <v>20300</v>
+        <v>25200</v>
       </c>
       <c r="G52" s="3">
-        <v>114100</v>
+        <v>20400</v>
       </c>
       <c r="H52" s="3">
-        <v>114300</v>
+        <v>114900</v>
       </c>
       <c r="I52" s="3">
-        <v>26500</v>
+        <v>115100</v>
       </c>
       <c r="J52" s="3">
+        <v>26700</v>
+      </c>
+      <c r="K52" s="3">
         <v>21600</v>
-      </c>
-      <c r="K52" s="3">
-        <v>3000</v>
       </c>
       <c r="L52" s="3">
         <v>3000</v>
       </c>
       <c r="M52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N52" s="3">
         <v>900</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>4103200</v>
+        <v>4286800</v>
       </c>
       <c r="E54" s="3">
-        <v>3921400</v>
+        <v>4131100</v>
       </c>
       <c r="F54" s="3">
-        <v>3276800</v>
+        <v>3948100</v>
       </c>
       <c r="G54" s="3">
-        <v>2645000</v>
+        <v>3299100</v>
       </c>
       <c r="H54" s="3">
-        <v>2175600</v>
+        <v>2663000</v>
       </c>
       <c r="I54" s="3">
-        <v>1697700</v>
+        <v>2190400</v>
       </c>
       <c r="J54" s="3">
+        <v>1709200</v>
+      </c>
+      <c r="K54" s="3">
         <v>1296900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1048200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>826400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>534400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>341400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>297100</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,176 +2654,189 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3700</v>
+        <v>3400</v>
       </c>
       <c r="E57" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F57" s="3">
         <v>4400</v>
       </c>
-      <c r="F57" s="3">
-        <v>11000</v>
-      </c>
       <c r="G57" s="3">
-        <v>5000</v>
+        <v>11100</v>
       </c>
       <c r="H57" s="3">
-        <v>2700</v>
+        <v>5100</v>
       </c>
       <c r="I57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3300</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
       <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
         <v>700</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>17</v>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>4300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>24400</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>400</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>556700</v>
+        <v>702200</v>
       </c>
       <c r="E59" s="3">
-        <v>546000</v>
+        <v>560500</v>
       </c>
       <c r="F59" s="3">
-        <v>566900</v>
+        <v>549700</v>
       </c>
       <c r="G59" s="3">
-        <v>542600</v>
+        <v>570800</v>
       </c>
       <c r="H59" s="3">
-        <v>572300</v>
+        <v>546300</v>
       </c>
       <c r="I59" s="3">
-        <v>535600</v>
+        <v>576200</v>
       </c>
       <c r="J59" s="3">
+        <v>539300</v>
+      </c>
+      <c r="K59" s="3">
         <v>503700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>272600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>169200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>119700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>48300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>29000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>560400</v>
+        <v>705600</v>
       </c>
       <c r="E60" s="3">
-        <v>550400</v>
+        <v>564200</v>
       </c>
       <c r="F60" s="3">
-        <v>578000</v>
+        <v>554200</v>
       </c>
       <c r="G60" s="3">
-        <v>547600</v>
+        <v>581900</v>
       </c>
       <c r="H60" s="3">
-        <v>575100</v>
+        <v>551300</v>
       </c>
       <c r="I60" s="3">
-        <v>537000</v>
+        <v>579000</v>
       </c>
       <c r="J60" s="3">
+        <v>540700</v>
+      </c>
+      <c r="K60" s="3">
         <v>351300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>300200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>169200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>120100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>48300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>29600</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2734,51 +2876,57 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>78500</v>
+        <v>81600</v>
       </c>
       <c r="E62" s="3">
-        <v>83600</v>
+        <v>79000</v>
       </c>
       <c r="F62" s="3">
-        <v>101700</v>
+        <v>84200</v>
       </c>
       <c r="G62" s="3">
-        <v>80600</v>
+        <v>102400</v>
       </c>
       <c r="H62" s="3">
-        <v>66300</v>
+        <v>81200</v>
       </c>
       <c r="I62" s="3">
-        <v>64900</v>
+        <v>66700</v>
       </c>
       <c r="J62" s="3">
+        <v>65400</v>
+      </c>
+      <c r="K62" s="3">
         <v>68600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>72700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>83400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>77700</v>
-      </c>
-      <c r="N62" s="3">
-        <v>69600</v>
       </c>
       <c r="O62" s="3">
         <v>69600</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>69600</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>804600</v>
+        <v>960300</v>
       </c>
       <c r="E66" s="3">
-        <v>797400</v>
+        <v>810100</v>
       </c>
       <c r="F66" s="3">
-        <v>843000</v>
+        <v>802800</v>
       </c>
       <c r="G66" s="3">
-        <v>625100</v>
+        <v>848700</v>
       </c>
       <c r="H66" s="3">
-        <v>638100</v>
+        <v>629300</v>
       </c>
       <c r="I66" s="3">
-        <v>599700</v>
+        <v>642400</v>
       </c>
       <c r="J66" s="3">
+        <v>603800</v>
+      </c>
+      <c r="K66" s="3">
         <v>418600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>372900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>252500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>197800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>117900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>99300</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>2236400</v>
+      <c r="D72" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E72" s="3">
-        <v>2045100</v>
+        <v>2251700</v>
       </c>
       <c r="F72" s="3">
-        <v>1859300</v>
+        <v>2059100</v>
       </c>
       <c r="G72" s="3">
-        <v>1477200</v>
+        <v>1872000</v>
       </c>
       <c r="H72" s="3">
-        <v>1035400</v>
+        <v>1487300</v>
       </c>
       <c r="I72" s="3">
-        <v>638900</v>
+        <v>1042400</v>
       </c>
       <c r="J72" s="3">
+        <v>643300</v>
+      </c>
+      <c r="K72" s="3">
         <v>444800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>277500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>157000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>38700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>60600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>37000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3298600</v>
+        <v>3326500</v>
       </c>
       <c r="E76" s="3">
-        <v>3124000</v>
+        <v>3321000</v>
       </c>
       <c r="F76" s="3">
-        <v>2433800</v>
+        <v>3145300</v>
       </c>
       <c r="G76" s="3">
-        <v>2020000</v>
+        <v>2450300</v>
       </c>
       <c r="H76" s="3">
-        <v>1537600</v>
+        <v>2033700</v>
       </c>
       <c r="I76" s="3">
-        <v>1098000</v>
+        <v>1548000</v>
       </c>
       <c r="J76" s="3">
+        <v>1105400</v>
+      </c>
+      <c r="K76" s="3">
         <v>878200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>675300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>573900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>336500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>223500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>197800</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>249500</v>
+        <v>261400</v>
       </c>
       <c r="E81" s="3">
-        <v>296700</v>
+        <v>251200</v>
       </c>
       <c r="F81" s="3">
-        <v>470200</v>
+        <v>298700</v>
       </c>
       <c r="G81" s="3">
-        <v>441900</v>
+        <v>473400</v>
       </c>
       <c r="H81" s="3">
-        <v>396400</v>
+        <v>444900</v>
       </c>
       <c r="I81" s="3">
-        <v>276400</v>
+        <v>399100</v>
       </c>
       <c r="J81" s="3">
+        <v>278300</v>
+      </c>
+      <c r="K81" s="3">
         <v>169600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>137900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>117200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>69400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>30500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>19100</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>42100</v>
+      <c r="D83" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E83" s="3">
-        <v>42700</v>
+        <v>42400</v>
       </c>
       <c r="F83" s="3">
-        <v>23500</v>
+        <v>43000</v>
       </c>
       <c r="G83" s="3">
-        <v>16400</v>
+        <v>23700</v>
       </c>
       <c r="H83" s="3">
-        <v>14100</v>
+        <v>16500</v>
       </c>
       <c r="I83" s="3">
-        <v>12300</v>
+        <v>14200</v>
       </c>
       <c r="J83" s="3">
+        <v>12400</v>
+      </c>
+      <c r="K83" s="3">
         <v>9600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5200</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>354200</v>
+      <c r="D89" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E89" s="3">
-        <v>486600</v>
+        <v>356600</v>
       </c>
       <c r="F89" s="3">
-        <v>459200</v>
+        <v>489900</v>
       </c>
       <c r="G89" s="3">
-        <v>399000</v>
+        <v>462300</v>
       </c>
       <c r="H89" s="3">
-        <v>429600</v>
+        <v>401700</v>
       </c>
       <c r="I89" s="3">
-        <v>340200</v>
+        <v>432600</v>
       </c>
       <c r="J89" s="3">
+        <v>342500</v>
+      </c>
+      <c r="K89" s="3">
         <v>217400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>203500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>160300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>90300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>40100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>21300</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-16100</v>
+      <c r="D91" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E91" s="3">
-        <v>-30200</v>
+        <v>-16200</v>
       </c>
       <c r="F91" s="3">
-        <v>-36400</v>
+        <v>-30400</v>
       </c>
       <c r="G91" s="3">
-        <v>-28200</v>
+        <v>-36700</v>
       </c>
       <c r="H91" s="3">
-        <v>-15700</v>
+        <v>-28400</v>
       </c>
       <c r="I91" s="3">
-        <v>-11900</v>
+        <v>-15800</v>
       </c>
       <c r="J91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-12300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12400</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-6700</v>
       </c>
       <c r="M91" s="3">
         <v>-6700</v>
       </c>
       <c r="N91" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="O91" s="3">
         <v>-4000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4600</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-429300</v>
+      <c r="D94" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E94" s="3">
-        <v>-526500</v>
+        <v>-432300</v>
       </c>
       <c r="F94" s="3">
-        <v>-412200</v>
+        <v>-530100</v>
       </c>
       <c r="G94" s="3">
-        <v>-161300</v>
+        <v>-415000</v>
       </c>
       <c r="H94" s="3">
-        <v>-455800</v>
+        <v>-162400</v>
       </c>
       <c r="I94" s="3">
-        <v>-678500</v>
+        <v>-458900</v>
       </c>
       <c r="J94" s="3">
+        <v>-683100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-71100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-56700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-275500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1800</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,28 +4220,29 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-58200</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-93000</v>
+        <v>-58600</v>
       </c>
       <c r="F96" s="3">
-        <v>-89900</v>
+        <v>-93600</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-90500</v>
       </c>
       <c r="H96" s="3">
-        <v>-82300</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-82800</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -4021,17 +4254,20 @@
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-33600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-6400</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>-157400</v>
+      <c r="D100" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E100" s="3">
-        <v>400200</v>
+        <v>-158500</v>
       </c>
       <c r="F100" s="3">
-        <v>-75500</v>
+        <v>402900</v>
       </c>
       <c r="G100" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="H100" s="3">
         <v>9500</v>
       </c>
-      <c r="H100" s="3">
-        <v>-75100</v>
-      </c>
       <c r="I100" s="3">
-        <v>8400</v>
+        <v>-75600</v>
       </c>
       <c r="J100" s="3">
+        <v>8500</v>
+      </c>
+      <c r="K100" s="3">
         <v>3900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>101400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>25800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-13700</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>23200</v>
+      <c r="D101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E101" s="3">
+        <v>23400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-6500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>5400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>-209300</v>
+      <c r="D102" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E102" s="3">
-        <v>353800</v>
+        <v>-210800</v>
       </c>
       <c r="F102" s="3">
-        <v>-31000</v>
+        <v>356200</v>
       </c>
       <c r="G102" s="3">
-        <v>245300</v>
+        <v>-31200</v>
       </c>
       <c r="H102" s="3">
-        <v>-95900</v>
+        <v>247000</v>
       </c>
       <c r="I102" s="3">
-        <v>-330200</v>
+        <v>-96600</v>
       </c>
       <c r="J102" s="3">
+        <v>-332500</v>
+      </c>
+      <c r="K102" s="3">
         <v>150400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>152900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>109200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>29700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5700</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ATHM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ATHM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>ATHM</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>998700</v>
+        <v>992600</v>
       </c>
       <c r="E8" s="3">
-        <v>964900</v>
+        <v>958900</v>
       </c>
       <c r="F8" s="3">
-        <v>1006100</v>
+        <v>999900</v>
       </c>
       <c r="G8" s="3">
-        <v>1203700</v>
+        <v>1196300</v>
       </c>
       <c r="H8" s="3">
-        <v>1170700</v>
+        <v>1163400</v>
       </c>
       <c r="I8" s="3">
-        <v>1005600</v>
+        <v>999300</v>
       </c>
       <c r="J8" s="3">
-        <v>863300</v>
+        <v>858000</v>
       </c>
       <c r="K8" s="3">
         <v>823200</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>196300</v>
+        <v>181900</v>
       </c>
       <c r="E9" s="3">
-        <v>158200</v>
+        <v>157200</v>
       </c>
       <c r="F9" s="3">
-        <v>140200</v>
+        <v>139400</v>
       </c>
       <c r="G9" s="3">
-        <v>120100</v>
+        <v>119400</v>
       </c>
       <c r="H9" s="3">
-        <v>107100</v>
+        <v>106400</v>
       </c>
       <c r="I9" s="3">
-        <v>81800</v>
+        <v>81300</v>
       </c>
       <c r="J9" s="3">
-        <v>121500</v>
+        <v>120700</v>
       </c>
       <c r="K9" s="3">
         <v>282200</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>802500</v>
+        <v>810600</v>
       </c>
       <c r="E10" s="3">
-        <v>806700</v>
+        <v>801700</v>
       </c>
       <c r="F10" s="3">
-        <v>865900</v>
+        <v>860500</v>
       </c>
       <c r="G10" s="3">
-        <v>1083600</v>
+        <v>1076900</v>
       </c>
       <c r="H10" s="3">
-        <v>1063600</v>
+        <v>1057000</v>
       </c>
       <c r="I10" s="3">
-        <v>923800</v>
+        <v>918000</v>
       </c>
       <c r="J10" s="3">
-        <v>741900</v>
+        <v>737300</v>
       </c>
       <c r="K10" s="3">
         <v>541000</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>187500</v>
+        <v>186300</v>
       </c>
       <c r="E12" s="3">
-        <v>197000</v>
+        <v>195800</v>
       </c>
       <c r="F12" s="3">
-        <v>194400</v>
+        <v>193200</v>
       </c>
       <c r="G12" s="3">
-        <v>189700</v>
+        <v>188500</v>
       </c>
       <c r="H12" s="3">
-        <v>179500</v>
+        <v>178400</v>
       </c>
       <c r="I12" s="3">
-        <v>157800</v>
+        <v>156800</v>
       </c>
       <c r="J12" s="3">
-        <v>122200</v>
+        <v>121400</v>
       </c>
       <c r="K12" s="3">
         <v>78900</v>
@@ -969,14 +969,14 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>17</v>
+      <c r="D14" s="3">
+        <v>-3800</v>
       </c>
       <c r="E14" s="3">
         <v>-7800</v>
       </c>
       <c r="F14" s="3">
-        <v>-7200</v>
+        <v>-7100</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>17</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>877300</v>
+        <v>868100</v>
       </c>
       <c r="E17" s="3">
-        <v>829200</v>
+        <v>824000</v>
       </c>
       <c r="F17" s="3">
-        <v>792100</v>
+        <v>787200</v>
       </c>
       <c r="G17" s="3">
-        <v>827700</v>
+        <v>822600</v>
       </c>
       <c r="H17" s="3">
-        <v>787200</v>
+        <v>782400</v>
       </c>
       <c r="I17" s="3">
-        <v>654200</v>
+        <v>650100</v>
       </c>
       <c r="J17" s="3">
-        <v>579300</v>
+        <v>575700</v>
       </c>
       <c r="K17" s="3">
         <v>663900</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>121400</v>
+        <v>124400</v>
       </c>
       <c r="E18" s="3">
-        <v>135700</v>
+        <v>134900</v>
       </c>
       <c r="F18" s="3">
-        <v>214000</v>
+        <v>212600</v>
       </c>
       <c r="G18" s="3">
-        <v>376000</v>
+        <v>373700</v>
       </c>
       <c r="H18" s="3">
-        <v>383400</v>
+        <v>381100</v>
       </c>
       <c r="I18" s="3">
-        <v>351400</v>
+        <v>349200</v>
       </c>
       <c r="J18" s="3">
-        <v>284100</v>
+        <v>282300</v>
       </c>
       <c r="K18" s="3">
         <v>159300</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>156300</v>
+        <v>151600</v>
       </c>
       <c r="E20" s="3">
-        <v>109300</v>
+        <v>108700</v>
       </c>
       <c r="F20" s="3">
-        <v>88700</v>
+        <v>88200</v>
       </c>
       <c r="G20" s="3">
-        <v>134000</v>
+        <v>133100</v>
       </c>
       <c r="H20" s="3">
-        <v>131100</v>
+        <v>130300</v>
       </c>
       <c r="I20" s="3">
-        <v>99200</v>
+        <v>98600</v>
       </c>
       <c r="J20" s="3">
-        <v>30300</v>
+        <v>30200</v>
       </c>
       <c r="K20" s="3">
         <v>13200</v>
@@ -1229,26 +1229,26 @@
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>17</v>
+      <c r="D21" s="3">
+        <v>309700</v>
       </c>
       <c r="E21" s="3">
-        <v>287500</v>
+        <v>285600</v>
       </c>
       <c r="F21" s="3">
-        <v>345700</v>
+        <v>343400</v>
       </c>
       <c r="G21" s="3">
-        <v>533700</v>
+        <v>530300</v>
       </c>
       <c r="H21" s="3">
-        <v>531000</v>
+        <v>527700</v>
       </c>
       <c r="I21" s="3">
-        <v>464800</v>
+        <v>461900</v>
       </c>
       <c r="J21" s="3">
-        <v>326800</v>
+        <v>324700</v>
       </c>
       <c r="K21" s="3">
         <v>182100</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>277700</v>
+        <v>276000</v>
       </c>
       <c r="E23" s="3">
-        <v>245100</v>
+        <v>243600</v>
       </c>
       <c r="F23" s="3">
-        <v>302700</v>
+        <v>300800</v>
       </c>
       <c r="G23" s="3">
-        <v>510000</v>
+        <v>506800</v>
       </c>
       <c r="H23" s="3">
-        <v>514500</v>
+        <v>511300</v>
       </c>
       <c r="I23" s="3">
-        <v>450600</v>
+        <v>447800</v>
       </c>
       <c r="J23" s="3">
-        <v>314400</v>
+        <v>312500</v>
       </c>
       <c r="K23" s="3">
         <v>172400</v>
@@ -1368,22 +1368,22 @@
         <v>10000</v>
       </c>
       <c r="E24" s="3">
-        <v>-8600</v>
+        <v>-8500</v>
       </c>
       <c r="F24" s="3">
         <v>4700</v>
       </c>
       <c r="G24" s="3">
-        <v>36300</v>
+        <v>36100</v>
       </c>
       <c r="H24" s="3">
-        <v>69600</v>
+        <v>69100</v>
       </c>
       <c r="I24" s="3">
-        <v>52500</v>
+        <v>52200</v>
       </c>
       <c r="J24" s="3">
-        <v>37100</v>
+        <v>36900</v>
       </c>
       <c r="K24" s="3">
         <v>4500</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>267700</v>
+        <v>266000</v>
       </c>
       <c r="E26" s="3">
-        <v>253700</v>
+        <v>252100</v>
       </c>
       <c r="F26" s="3">
-        <v>297900</v>
+        <v>296100</v>
       </c>
       <c r="G26" s="3">
-        <v>473700</v>
+        <v>470800</v>
       </c>
       <c r="H26" s="3">
-        <v>445000</v>
+        <v>442200</v>
       </c>
       <c r="I26" s="3">
-        <v>398100</v>
+        <v>395600</v>
       </c>
       <c r="J26" s="3">
-        <v>277300</v>
+        <v>275600</v>
       </c>
       <c r="K26" s="3">
         <v>167900</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>261400</v>
+        <v>259800</v>
       </c>
       <c r="E27" s="3">
-        <v>251200</v>
+        <v>249700</v>
       </c>
       <c r="F27" s="3">
-        <v>298700</v>
+        <v>296800</v>
       </c>
       <c r="G27" s="3">
-        <v>473400</v>
+        <v>470500</v>
       </c>
       <c r="H27" s="3">
-        <v>444900</v>
+        <v>442100</v>
       </c>
       <c r="I27" s="3">
-        <v>399100</v>
+        <v>396700</v>
       </c>
       <c r="J27" s="3">
-        <v>278300</v>
+        <v>276500</v>
       </c>
       <c r="K27" s="3">
         <v>169600</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-156300</v>
+        <v>-151600</v>
       </c>
       <c r="E32" s="3">
-        <v>-109300</v>
+        <v>-108700</v>
       </c>
       <c r="F32" s="3">
-        <v>-88700</v>
+        <v>-88200</v>
       </c>
       <c r="G32" s="3">
-        <v>-134000</v>
+        <v>-133100</v>
       </c>
       <c r="H32" s="3">
-        <v>-131100</v>
+        <v>-130300</v>
       </c>
       <c r="I32" s="3">
-        <v>-99200</v>
+        <v>-98600</v>
       </c>
       <c r="J32" s="3">
-        <v>-30300</v>
+        <v>-30200</v>
       </c>
       <c r="K32" s="3">
         <v>-13200</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>261400</v>
+        <v>259800</v>
       </c>
       <c r="E33" s="3">
-        <v>251200</v>
+        <v>249700</v>
       </c>
       <c r="F33" s="3">
-        <v>298700</v>
+        <v>296800</v>
       </c>
       <c r="G33" s="3">
-        <v>473400</v>
+        <v>470500</v>
       </c>
       <c r="H33" s="3">
-        <v>444900</v>
+        <v>442100</v>
       </c>
       <c r="I33" s="3">
-        <v>399100</v>
+        <v>396700</v>
       </c>
       <c r="J33" s="3">
-        <v>278300</v>
+        <v>276500</v>
       </c>
       <c r="K33" s="3">
         <v>169600</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>261400</v>
+        <v>259800</v>
       </c>
       <c r="E35" s="3">
-        <v>251200</v>
+        <v>249700</v>
       </c>
       <c r="F35" s="3">
-        <v>298700</v>
+        <v>296800</v>
       </c>
       <c r="G35" s="3">
-        <v>473400</v>
+        <v>470500</v>
       </c>
       <c r="H35" s="3">
-        <v>444900</v>
+        <v>442100</v>
       </c>
       <c r="I35" s="3">
-        <v>399100</v>
+        <v>396700</v>
       </c>
       <c r="J35" s="3">
-        <v>278300</v>
+        <v>276500</v>
       </c>
       <c r="K35" s="3">
         <v>169600</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>694600</v>
+        <v>690300</v>
       </c>
       <c r="E41" s="3">
-        <v>389400</v>
+        <v>387000</v>
       </c>
       <c r="F41" s="3">
-        <v>589000</v>
+        <v>585300</v>
       </c>
       <c r="G41" s="3">
-        <v>243500</v>
+        <v>241900</v>
       </c>
       <c r="H41" s="3">
-        <v>276400</v>
+        <v>274700</v>
       </c>
       <c r="I41" s="3">
-        <v>29500</v>
+        <v>29300</v>
       </c>
       <c r="J41" s="3">
-        <v>126700</v>
+        <v>125900</v>
       </c>
       <c r="K41" s="3">
         <v>454800</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2579100</v>
+        <v>2565100</v>
       </c>
       <c r="E42" s="3">
-        <v>2683100</v>
+        <v>2666500</v>
       </c>
       <c r="F42" s="3">
-        <v>2296100</v>
+        <v>2281900</v>
       </c>
       <c r="G42" s="3">
-        <v>1791800</v>
+        <v>1780800</v>
       </c>
       <c r="H42" s="3">
-        <v>1505100</v>
+        <v>1495700</v>
       </c>
       <c r="I42" s="3">
-        <v>1370200</v>
+        <v>1361700</v>
       </c>
       <c r="J42" s="3">
-        <v>1008500</v>
+        <v>1002300</v>
       </c>
       <c r="K42" s="3">
         <v>335800</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>207000</v>
+        <v>211400</v>
       </c>
       <c r="E43" s="3">
-        <v>280600</v>
+        <v>278900</v>
       </c>
       <c r="F43" s="3">
-        <v>314900</v>
+        <v>312900</v>
       </c>
       <c r="G43" s="3">
-        <v>440900</v>
+        <v>438200</v>
       </c>
       <c r="H43" s="3">
-        <v>453300</v>
+        <v>450500</v>
       </c>
       <c r="I43" s="3">
-        <v>393400</v>
+        <v>391000</v>
       </c>
       <c r="J43" s="3">
-        <v>266700</v>
+        <v>265000</v>
       </c>
       <c r="K43" s="3">
         <v>342900</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>67800</v>
+        <v>59700</v>
       </c>
       <c r="E45" s="3">
-        <v>42400</v>
+        <v>42100</v>
       </c>
       <c r="F45" s="3">
-        <v>42800</v>
+        <v>42500</v>
       </c>
       <c r="G45" s="3">
-        <v>76800</v>
+        <v>76300</v>
       </c>
       <c r="H45" s="3">
-        <v>39300</v>
+        <v>39100</v>
       </c>
       <c r="I45" s="3">
-        <v>33800</v>
+        <v>33600</v>
       </c>
       <c r="J45" s="3">
-        <v>24200</v>
+        <v>24100</v>
       </c>
       <c r="K45" s="3">
         <v>111900</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3548500</v>
+        <v>3526500</v>
       </c>
       <c r="E46" s="3">
-        <v>3395600</v>
+        <v>3374500</v>
       </c>
       <c r="F46" s="3">
-        <v>3242700</v>
+        <v>3222700</v>
       </c>
       <c r="G46" s="3">
-        <v>2553000</v>
+        <v>2537200</v>
       </c>
       <c r="H46" s="3">
-        <v>2274100</v>
+        <v>2260100</v>
       </c>
       <c r="I46" s="3">
-        <v>1826900</v>
+        <v>1815600</v>
       </c>
       <c r="J46" s="3">
-        <v>1426100</v>
+        <v>1417300</v>
       </c>
       <c r="K46" s="3">
         <v>1026300</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>64600</v>
+        <v>64200</v>
       </c>
       <c r="E47" s="3">
-        <v>59600</v>
+        <v>59200</v>
       </c>
       <c r="F47" s="3">
-        <v>10900</v>
+        <v>10800</v>
       </c>
       <c r="G47" s="3">
-        <v>12300</v>
+        <v>12200</v>
       </c>
       <c r="H47" s="3">
-        <v>10600</v>
+        <v>10500</v>
       </c>
       <c r="I47" s="3">
-        <v>10200</v>
+        <v>10100</v>
       </c>
       <c r="J47" s="3">
-        <v>22100</v>
+        <v>22000</v>
       </c>
       <c r="K47" s="3">
         <v>18700</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>27900</v>
+        <v>55300</v>
       </c>
       <c r="E48" s="3">
-        <v>51500</v>
+        <v>51200</v>
       </c>
       <c r="F48" s="3">
-        <v>71600</v>
+        <v>71100</v>
       </c>
       <c r="G48" s="3">
-        <v>86100</v>
+        <v>85600</v>
       </c>
       <c r="H48" s="3">
-        <v>50400</v>
+        <v>50100</v>
       </c>
       <c r="I48" s="3">
-        <v>23700</v>
+        <v>23500</v>
       </c>
       <c r="J48" s="3">
-        <v>18100</v>
+        <v>18000</v>
       </c>
       <c r="K48" s="3">
         <v>37200</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>576100</v>
+        <v>572500</v>
       </c>
       <c r="E49" s="3">
-        <v>586700</v>
+        <v>583100</v>
       </c>
       <c r="F49" s="3">
-        <v>597700</v>
+        <v>594000</v>
       </c>
       <c r="G49" s="3">
-        <v>627200</v>
+        <v>623400</v>
       </c>
       <c r="H49" s="3">
-        <v>213000</v>
+        <v>211700</v>
       </c>
       <c r="I49" s="3">
-        <v>214600</v>
+        <v>213300</v>
       </c>
       <c r="J49" s="3">
-        <v>216200</v>
+        <v>214900</v>
       </c>
       <c r="K49" s="3">
         <v>423600</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>69700</v>
+        <v>41800</v>
       </c>
       <c r="E52" s="3">
-        <v>37700</v>
+        <v>37500</v>
       </c>
       <c r="F52" s="3">
-        <v>25200</v>
+        <v>25100</v>
       </c>
       <c r="G52" s="3">
-        <v>20400</v>
+        <v>20300</v>
       </c>
       <c r="H52" s="3">
-        <v>114900</v>
+        <v>114200</v>
       </c>
       <c r="I52" s="3">
-        <v>115100</v>
+        <v>114400</v>
       </c>
       <c r="J52" s="3">
-        <v>26700</v>
+        <v>26500</v>
       </c>
       <c r="K52" s="3">
         <v>21600</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>4286800</v>
+        <v>4260300</v>
       </c>
       <c r="E54" s="3">
-        <v>4131100</v>
+        <v>4105500</v>
       </c>
       <c r="F54" s="3">
-        <v>3948100</v>
+        <v>3923700</v>
       </c>
       <c r="G54" s="3">
-        <v>3299100</v>
+        <v>3278700</v>
       </c>
       <c r="H54" s="3">
-        <v>2663000</v>
+        <v>2646600</v>
       </c>
       <c r="I54" s="3">
-        <v>2190400</v>
+        <v>2176900</v>
       </c>
       <c r="J54" s="3">
-        <v>1709200</v>
+        <v>1698700</v>
       </c>
       <c r="K54" s="3">
         <v>1296900</v>
@@ -2664,19 +2664,19 @@
         <v>3400</v>
       </c>
       <c r="E57" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="F57" s="3">
         <v>4400</v>
       </c>
       <c r="G57" s="3">
-        <v>11100</v>
+        <v>11000</v>
       </c>
       <c r="H57" s="3">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="I57" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="J57" s="3">
         <v>1400</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>702200</v>
+        <v>697800</v>
       </c>
       <c r="E59" s="3">
-        <v>560500</v>
+        <v>557000</v>
       </c>
       <c r="F59" s="3">
-        <v>549700</v>
+        <v>546300</v>
       </c>
       <c r="G59" s="3">
-        <v>570800</v>
+        <v>567300</v>
       </c>
       <c r="H59" s="3">
-        <v>546300</v>
+        <v>542900</v>
       </c>
       <c r="I59" s="3">
-        <v>576200</v>
+        <v>572700</v>
       </c>
       <c r="J59" s="3">
-        <v>539300</v>
+        <v>535900</v>
       </c>
       <c r="K59" s="3">
         <v>503700</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>705600</v>
+        <v>701200</v>
       </c>
       <c r="E60" s="3">
-        <v>564200</v>
+        <v>560700</v>
       </c>
       <c r="F60" s="3">
-        <v>554200</v>
+        <v>550700</v>
       </c>
       <c r="G60" s="3">
-        <v>581900</v>
+        <v>578300</v>
       </c>
       <c r="H60" s="3">
-        <v>551300</v>
+        <v>547900</v>
       </c>
       <c r="I60" s="3">
-        <v>579000</v>
+        <v>575400</v>
       </c>
       <c r="J60" s="3">
-        <v>540700</v>
+        <v>537300</v>
       </c>
       <c r="K60" s="3">
         <v>351300</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>81600</v>
+        <v>81100</v>
       </c>
       <c r="E62" s="3">
-        <v>79000</v>
+        <v>78500</v>
       </c>
       <c r="F62" s="3">
-        <v>84200</v>
+        <v>83600</v>
       </c>
       <c r="G62" s="3">
-        <v>102400</v>
+        <v>101700</v>
       </c>
       <c r="H62" s="3">
-        <v>81200</v>
+        <v>80700</v>
       </c>
       <c r="I62" s="3">
-        <v>66700</v>
+        <v>66300</v>
       </c>
       <c r="J62" s="3">
-        <v>65400</v>
+        <v>65000</v>
       </c>
       <c r="K62" s="3">
         <v>68600</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>960300</v>
+        <v>954300</v>
       </c>
       <c r="E66" s="3">
-        <v>810100</v>
+        <v>805100</v>
       </c>
       <c r="F66" s="3">
-        <v>802800</v>
+        <v>797800</v>
       </c>
       <c r="G66" s="3">
-        <v>848700</v>
+        <v>843500</v>
       </c>
       <c r="H66" s="3">
-        <v>629300</v>
+        <v>625400</v>
       </c>
       <c r="I66" s="3">
-        <v>642400</v>
+        <v>638400</v>
       </c>
       <c r="J66" s="3">
-        <v>603800</v>
+        <v>600100</v>
       </c>
       <c r="K66" s="3">
         <v>418600</v>
@@ -3309,26 +3309,26 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>17</v>
+      <c r="D72" s="3">
+        <v>2293700</v>
       </c>
       <c r="E72" s="3">
-        <v>2251700</v>
+        <v>2237700</v>
       </c>
       <c r="F72" s="3">
-        <v>2059100</v>
+        <v>2046300</v>
       </c>
       <c r="G72" s="3">
-        <v>1872000</v>
+        <v>1860400</v>
       </c>
       <c r="H72" s="3">
-        <v>1487300</v>
+        <v>1478100</v>
       </c>
       <c r="I72" s="3">
-        <v>1042400</v>
+        <v>1036000</v>
       </c>
       <c r="J72" s="3">
-        <v>643300</v>
+        <v>639300</v>
       </c>
       <c r="K72" s="3">
         <v>444800</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3326500</v>
+        <v>3305900</v>
       </c>
       <c r="E76" s="3">
-        <v>3321000</v>
+        <v>3300500</v>
       </c>
       <c r="F76" s="3">
-        <v>3145300</v>
+        <v>3125800</v>
       </c>
       <c r="G76" s="3">
-        <v>2450300</v>
+        <v>2435200</v>
       </c>
       <c r="H76" s="3">
-        <v>2033700</v>
+        <v>2021200</v>
       </c>
       <c r="I76" s="3">
-        <v>1548000</v>
+        <v>1538500</v>
       </c>
       <c r="J76" s="3">
-        <v>1105400</v>
+        <v>1098600</v>
       </c>
       <c r="K76" s="3">
         <v>878200</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>261400</v>
+        <v>259800</v>
       </c>
       <c r="E81" s="3">
-        <v>251200</v>
+        <v>249700</v>
       </c>
       <c r="F81" s="3">
-        <v>298700</v>
+        <v>296800</v>
       </c>
       <c r="G81" s="3">
-        <v>473400</v>
+        <v>470500</v>
       </c>
       <c r="H81" s="3">
-        <v>444900</v>
+        <v>442100</v>
       </c>
       <c r="I81" s="3">
-        <v>399100</v>
+        <v>396700</v>
       </c>
       <c r="J81" s="3">
-        <v>278300</v>
+        <v>276500</v>
       </c>
       <c r="K81" s="3">
         <v>169600</v>
@@ -3693,26 +3693,26 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>17</v>
+      <c r="D83" s="3">
+        <v>33800</v>
       </c>
       <c r="E83" s="3">
-        <v>42400</v>
+        <v>42200</v>
       </c>
       <c r="F83" s="3">
-        <v>43000</v>
+        <v>42700</v>
       </c>
       <c r="G83" s="3">
-        <v>23700</v>
+        <v>23500</v>
       </c>
       <c r="H83" s="3">
-        <v>16500</v>
+        <v>16400</v>
       </c>
       <c r="I83" s="3">
-        <v>14200</v>
+        <v>14100</v>
       </c>
       <c r="J83" s="3">
-        <v>12400</v>
+        <v>12300</v>
       </c>
       <c r="K83" s="3">
         <v>9600</v>
@@ -3963,26 +3963,26 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>17</v>
+      <c r="D89" s="3">
+        <v>338700</v>
       </c>
       <c r="E89" s="3">
-        <v>356600</v>
+        <v>354400</v>
       </c>
       <c r="F89" s="3">
-        <v>489900</v>
+        <v>486900</v>
       </c>
       <c r="G89" s="3">
-        <v>462300</v>
+        <v>459500</v>
       </c>
       <c r="H89" s="3">
-        <v>401700</v>
+        <v>399200</v>
       </c>
       <c r="I89" s="3">
-        <v>432600</v>
+        <v>429900</v>
       </c>
       <c r="J89" s="3">
-        <v>342500</v>
+        <v>340400</v>
       </c>
       <c r="K89" s="3">
         <v>217400</v>
@@ -4027,26 +4027,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>17</v>
+      <c r="D91" s="3">
+        <v>-10900</v>
       </c>
       <c r="E91" s="3">
-        <v>-16200</v>
+        <v>-16100</v>
       </c>
       <c r="F91" s="3">
-        <v>-30400</v>
+        <v>-30200</v>
       </c>
       <c r="G91" s="3">
-        <v>-36700</v>
+        <v>-36500</v>
       </c>
       <c r="H91" s="3">
-        <v>-28400</v>
+        <v>-28200</v>
       </c>
       <c r="I91" s="3">
-        <v>-15800</v>
+        <v>-15700</v>
       </c>
       <c r="J91" s="3">
-        <v>-12000</v>
+        <v>-11900</v>
       </c>
       <c r="K91" s="3">
         <v>-12300</v>
@@ -4162,26 +4162,26 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>17</v>
+      <c r="D94" s="3">
+        <v>138200</v>
       </c>
       <c r="E94" s="3">
-        <v>-432300</v>
+        <v>-429600</v>
       </c>
       <c r="F94" s="3">
-        <v>-530100</v>
+        <v>-526800</v>
       </c>
       <c r="G94" s="3">
-        <v>-415000</v>
+        <v>-412500</v>
       </c>
       <c r="H94" s="3">
-        <v>-162400</v>
+        <v>-161400</v>
       </c>
       <c r="I94" s="3">
-        <v>-458900</v>
+        <v>-456100</v>
       </c>
       <c r="J94" s="3">
-        <v>-683100</v>
+        <v>-678900</v>
       </c>
       <c r="K94" s="3">
         <v>-71100</v>
@@ -4227,22 +4227,22 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-67800</v>
       </c>
       <c r="E96" s="3">
-        <v>-58600</v>
+        <v>-58300</v>
       </c>
       <c r="F96" s="3">
-        <v>-93600</v>
+        <v>-93000</v>
       </c>
       <c r="G96" s="3">
-        <v>-90500</v>
+        <v>-90000</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-82800</v>
+        <v>-82300</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -4406,26 +4406,26 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>17</v>
+      <c r="D100" s="3">
+        <v>-155400</v>
       </c>
       <c r="E100" s="3">
-        <v>-158500</v>
+        <v>-157500</v>
       </c>
       <c r="F100" s="3">
-        <v>402900</v>
+        <v>400400</v>
       </c>
       <c r="G100" s="3">
-        <v>-76000</v>
+        <v>-75600</v>
       </c>
       <c r="H100" s="3">
         <v>9500</v>
       </c>
       <c r="I100" s="3">
-        <v>-75600</v>
+        <v>-75200</v>
       </c>
       <c r="J100" s="3">
-        <v>8500</v>
+        <v>8400</v>
       </c>
       <c r="K100" s="3">
         <v>3900</v>
@@ -4451,11 +4451,11 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>17</v>
+      <c r="D101" s="3">
+        <v>-2000</v>
       </c>
       <c r="E101" s="3">
-        <v>23400</v>
+        <v>23300</v>
       </c>
       <c r="F101" s="3">
         <v>-6500</v>
@@ -4496,26 +4496,26 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>17</v>
+      <c r="D102" s="3">
+        <v>319500</v>
       </c>
       <c r="E102" s="3">
-        <v>-210800</v>
+        <v>-209500</v>
       </c>
       <c r="F102" s="3">
-        <v>356200</v>
+        <v>354000</v>
       </c>
       <c r="G102" s="3">
-        <v>-31200</v>
+        <v>-31000</v>
       </c>
       <c r="H102" s="3">
-        <v>247000</v>
+        <v>245400</v>
       </c>
       <c r="I102" s="3">
-        <v>-96600</v>
+        <v>-96000</v>
       </c>
       <c r="J102" s="3">
-        <v>-332500</v>
+        <v>-330400</v>
       </c>
       <c r="K102" s="3">
         <v>150400</v>

--- a/AAII_Financials/Yearly/ATHM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ATHM_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>992600</v>
+        <v>1012800</v>
       </c>
       <c r="E8" s="3">
-        <v>958900</v>
+        <v>978500</v>
       </c>
       <c r="F8" s="3">
-        <v>999900</v>
+        <v>1020300</v>
       </c>
       <c r="G8" s="3">
-        <v>1196300</v>
+        <v>1220700</v>
       </c>
       <c r="H8" s="3">
-        <v>1163400</v>
+        <v>1187200</v>
       </c>
       <c r="I8" s="3">
-        <v>999300</v>
+        <v>1019700</v>
       </c>
       <c r="J8" s="3">
-        <v>858000</v>
+        <v>875500</v>
       </c>
       <c r="K8" s="3">
         <v>823200</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>181900</v>
+        <v>185600</v>
       </c>
       <c r="E9" s="3">
-        <v>157200</v>
+        <v>160400</v>
       </c>
       <c r="F9" s="3">
-        <v>139400</v>
+        <v>142200</v>
       </c>
       <c r="G9" s="3">
-        <v>119400</v>
+        <v>121800</v>
       </c>
       <c r="H9" s="3">
-        <v>106400</v>
+        <v>108600</v>
       </c>
       <c r="I9" s="3">
-        <v>81300</v>
+        <v>82900</v>
       </c>
       <c r="J9" s="3">
-        <v>120700</v>
+        <v>123200</v>
       </c>
       <c r="K9" s="3">
         <v>282200</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>810600</v>
+        <v>827200</v>
       </c>
       <c r="E10" s="3">
-        <v>801700</v>
+        <v>818100</v>
       </c>
       <c r="F10" s="3">
-        <v>860500</v>
+        <v>878100</v>
       </c>
       <c r="G10" s="3">
-        <v>1076900</v>
+        <v>1098800</v>
       </c>
       <c r="H10" s="3">
-        <v>1057000</v>
+        <v>1078600</v>
       </c>
       <c r="I10" s="3">
-        <v>918000</v>
+        <v>936800</v>
       </c>
       <c r="J10" s="3">
-        <v>737300</v>
+        <v>752300</v>
       </c>
       <c r="K10" s="3">
         <v>541000</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>186300</v>
+        <v>190100</v>
       </c>
       <c r="E12" s="3">
-        <v>195800</v>
+        <v>199800</v>
       </c>
       <c r="F12" s="3">
-        <v>193200</v>
+        <v>197100</v>
       </c>
       <c r="G12" s="3">
-        <v>188500</v>
+        <v>192300</v>
       </c>
       <c r="H12" s="3">
-        <v>178400</v>
+        <v>182000</v>
       </c>
       <c r="I12" s="3">
-        <v>156800</v>
+        <v>160000</v>
       </c>
       <c r="J12" s="3">
-        <v>121400</v>
+        <v>123900</v>
       </c>
       <c r="K12" s="3">
         <v>78900</v>
@@ -973,10 +973,10 @@
         <v>-3800</v>
       </c>
       <c r="E14" s="3">
-        <v>-7800</v>
+        <v>-8000</v>
       </c>
       <c r="F14" s="3">
-        <v>-7100</v>
+        <v>-7300</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>17</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>868100</v>
+        <v>885900</v>
       </c>
       <c r="E17" s="3">
-        <v>824000</v>
+        <v>840900</v>
       </c>
       <c r="F17" s="3">
-        <v>787200</v>
+        <v>803300</v>
       </c>
       <c r="G17" s="3">
-        <v>822600</v>
+        <v>839400</v>
       </c>
       <c r="H17" s="3">
-        <v>782400</v>
+        <v>798300</v>
       </c>
       <c r="I17" s="3">
-        <v>650100</v>
+        <v>663400</v>
       </c>
       <c r="J17" s="3">
-        <v>575700</v>
+        <v>587500</v>
       </c>
       <c r="K17" s="3">
         <v>663900</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>124400</v>
+        <v>127000</v>
       </c>
       <c r="E18" s="3">
-        <v>134900</v>
+        <v>137700</v>
       </c>
       <c r="F18" s="3">
-        <v>212600</v>
+        <v>217000</v>
       </c>
       <c r="G18" s="3">
-        <v>373700</v>
+        <v>381300</v>
       </c>
       <c r="H18" s="3">
-        <v>381100</v>
+        <v>388800</v>
       </c>
       <c r="I18" s="3">
-        <v>349200</v>
+        <v>356300</v>
       </c>
       <c r="J18" s="3">
-        <v>282300</v>
+        <v>288100</v>
       </c>
       <c r="K18" s="3">
         <v>159300</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>151600</v>
+        <v>154700</v>
       </c>
       <c r="E20" s="3">
-        <v>108700</v>
+        <v>110900</v>
       </c>
       <c r="F20" s="3">
-        <v>88200</v>
+        <v>90000</v>
       </c>
       <c r="G20" s="3">
-        <v>133100</v>
+        <v>135900</v>
       </c>
       <c r="H20" s="3">
-        <v>130300</v>
+        <v>132900</v>
       </c>
       <c r="I20" s="3">
-        <v>98600</v>
+        <v>100600</v>
       </c>
       <c r="J20" s="3">
-        <v>30200</v>
+        <v>30800</v>
       </c>
       <c r="K20" s="3">
         <v>13200</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>309700</v>
+        <v>316000</v>
       </c>
       <c r="E21" s="3">
-        <v>285600</v>
+        <v>291400</v>
       </c>
       <c r="F21" s="3">
-        <v>343400</v>
+        <v>350400</v>
       </c>
       <c r="G21" s="3">
-        <v>530300</v>
+        <v>541100</v>
       </c>
       <c r="H21" s="3">
-        <v>527700</v>
+        <v>538400</v>
       </c>
       <c r="I21" s="3">
-        <v>461900</v>
+        <v>471300</v>
       </c>
       <c r="J21" s="3">
-        <v>324700</v>
+        <v>331300</v>
       </c>
       <c r="K21" s="3">
         <v>182100</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>276000</v>
+        <v>281600</v>
       </c>
       <c r="E23" s="3">
-        <v>243600</v>
+        <v>248500</v>
       </c>
       <c r="F23" s="3">
-        <v>300800</v>
+        <v>306900</v>
       </c>
       <c r="G23" s="3">
-        <v>506800</v>
+        <v>517200</v>
       </c>
       <c r="H23" s="3">
-        <v>511300</v>
+        <v>521800</v>
       </c>
       <c r="I23" s="3">
-        <v>447800</v>
+        <v>457000</v>
       </c>
       <c r="J23" s="3">
-        <v>312500</v>
+        <v>318800</v>
       </c>
       <c r="K23" s="3">
         <v>172400</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>10000</v>
+        <v>10200</v>
       </c>
       <c r="E24" s="3">
-        <v>-8500</v>
+        <v>-8700</v>
       </c>
       <c r="F24" s="3">
-        <v>4700</v>
+        <v>4800</v>
       </c>
       <c r="G24" s="3">
-        <v>36100</v>
+        <v>36800</v>
       </c>
       <c r="H24" s="3">
-        <v>69100</v>
+        <v>70500</v>
       </c>
       <c r="I24" s="3">
-        <v>52200</v>
+        <v>53300</v>
       </c>
       <c r="J24" s="3">
-        <v>36900</v>
+        <v>37700</v>
       </c>
       <c r="K24" s="3">
         <v>4500</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>266000</v>
+        <v>271400</v>
       </c>
       <c r="E26" s="3">
-        <v>252100</v>
+        <v>257200</v>
       </c>
       <c r="F26" s="3">
-        <v>296100</v>
+        <v>302100</v>
       </c>
       <c r="G26" s="3">
-        <v>470800</v>
+        <v>480400</v>
       </c>
       <c r="H26" s="3">
-        <v>442200</v>
+        <v>451200</v>
       </c>
       <c r="I26" s="3">
-        <v>395600</v>
+        <v>403700</v>
       </c>
       <c r="J26" s="3">
-        <v>275600</v>
+        <v>281200</v>
       </c>
       <c r="K26" s="3">
         <v>167900</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>259800</v>
+        <v>265100</v>
       </c>
       <c r="E27" s="3">
-        <v>249700</v>
+        <v>254800</v>
       </c>
       <c r="F27" s="3">
-        <v>296800</v>
+        <v>302900</v>
       </c>
       <c r="G27" s="3">
-        <v>470500</v>
+        <v>480100</v>
       </c>
       <c r="H27" s="3">
-        <v>442100</v>
+        <v>451100</v>
       </c>
       <c r="I27" s="3">
-        <v>396700</v>
+        <v>404800</v>
       </c>
       <c r="J27" s="3">
-        <v>276500</v>
+        <v>282200</v>
       </c>
       <c r="K27" s="3">
         <v>169600</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-151600</v>
+        <v>-154700</v>
       </c>
       <c r="E32" s="3">
-        <v>-108700</v>
+        <v>-110900</v>
       </c>
       <c r="F32" s="3">
-        <v>-88200</v>
+        <v>-90000</v>
       </c>
       <c r="G32" s="3">
-        <v>-133100</v>
+        <v>-135900</v>
       </c>
       <c r="H32" s="3">
-        <v>-130300</v>
+        <v>-132900</v>
       </c>
       <c r="I32" s="3">
-        <v>-98600</v>
+        <v>-100600</v>
       </c>
       <c r="J32" s="3">
-        <v>-30200</v>
+        <v>-30800</v>
       </c>
       <c r="K32" s="3">
         <v>-13200</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>259800</v>
+        <v>265100</v>
       </c>
       <c r="E33" s="3">
-        <v>249700</v>
+        <v>254800</v>
       </c>
       <c r="F33" s="3">
-        <v>296800</v>
+        <v>302900</v>
       </c>
       <c r="G33" s="3">
-        <v>470500</v>
+        <v>480100</v>
       </c>
       <c r="H33" s="3">
-        <v>442100</v>
+        <v>451100</v>
       </c>
       <c r="I33" s="3">
-        <v>396700</v>
+        <v>404800</v>
       </c>
       <c r="J33" s="3">
-        <v>276500</v>
+        <v>282200</v>
       </c>
       <c r="K33" s="3">
         <v>169600</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>259800</v>
+        <v>265100</v>
       </c>
       <c r="E35" s="3">
-        <v>249700</v>
+        <v>254800</v>
       </c>
       <c r="F35" s="3">
-        <v>296800</v>
+        <v>302900</v>
       </c>
       <c r="G35" s="3">
-        <v>470500</v>
+        <v>480100</v>
       </c>
       <c r="H35" s="3">
-        <v>442100</v>
+        <v>451100</v>
       </c>
       <c r="I35" s="3">
-        <v>396700</v>
+        <v>404800</v>
       </c>
       <c r="J35" s="3">
-        <v>276500</v>
+        <v>282200</v>
       </c>
       <c r="K35" s="3">
         <v>169600</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>690300</v>
+        <v>704400</v>
       </c>
       <c r="E41" s="3">
-        <v>387000</v>
+        <v>394900</v>
       </c>
       <c r="F41" s="3">
-        <v>585300</v>
+        <v>597300</v>
       </c>
       <c r="G41" s="3">
-        <v>241900</v>
+        <v>246900</v>
       </c>
       <c r="H41" s="3">
-        <v>274700</v>
+        <v>280300</v>
       </c>
       <c r="I41" s="3">
-        <v>29300</v>
+        <v>29900</v>
       </c>
       <c r="J41" s="3">
-        <v>125900</v>
+        <v>128500</v>
       </c>
       <c r="K41" s="3">
         <v>454800</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2565100</v>
+        <v>2617500</v>
       </c>
       <c r="E42" s="3">
-        <v>2666500</v>
+        <v>2720900</v>
       </c>
       <c r="F42" s="3">
-        <v>2281900</v>
+        <v>2328500</v>
       </c>
       <c r="G42" s="3">
-        <v>1780800</v>
+        <v>1817100</v>
       </c>
       <c r="H42" s="3">
-        <v>1495700</v>
+        <v>1526300</v>
       </c>
       <c r="I42" s="3">
-        <v>1361700</v>
+        <v>1389500</v>
       </c>
       <c r="J42" s="3">
-        <v>1002300</v>
+        <v>1022700</v>
       </c>
       <c r="K42" s="3">
         <v>335800</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>211400</v>
+        <v>215700</v>
       </c>
       <c r="E43" s="3">
-        <v>278900</v>
+        <v>284600</v>
       </c>
       <c r="F43" s="3">
-        <v>312900</v>
+        <v>319300</v>
       </c>
       <c r="G43" s="3">
-        <v>438200</v>
+        <v>447100</v>
       </c>
       <c r="H43" s="3">
-        <v>450500</v>
+        <v>459700</v>
       </c>
       <c r="I43" s="3">
-        <v>391000</v>
+        <v>399000</v>
       </c>
       <c r="J43" s="3">
-        <v>265000</v>
+        <v>270400</v>
       </c>
       <c r="K43" s="3">
         <v>342900</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>59700</v>
+        <v>60900</v>
       </c>
       <c r="E45" s="3">
-        <v>42100</v>
+        <v>43000</v>
       </c>
       <c r="F45" s="3">
-        <v>42500</v>
+        <v>43400</v>
       </c>
       <c r="G45" s="3">
-        <v>76300</v>
+        <v>77900</v>
       </c>
       <c r="H45" s="3">
-        <v>39100</v>
+        <v>39900</v>
       </c>
       <c r="I45" s="3">
-        <v>33600</v>
+        <v>34300</v>
       </c>
       <c r="J45" s="3">
-        <v>24100</v>
+        <v>24600</v>
       </c>
       <c r="K45" s="3">
         <v>111900</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3526500</v>
+        <v>3598500</v>
       </c>
       <c r="E46" s="3">
-        <v>3374500</v>
+        <v>3443400</v>
       </c>
       <c r="F46" s="3">
-        <v>3222700</v>
+        <v>3288500</v>
       </c>
       <c r="G46" s="3">
-        <v>2537200</v>
+        <v>2589000</v>
       </c>
       <c r="H46" s="3">
-        <v>2260100</v>
+        <v>2306200</v>
       </c>
       <c r="I46" s="3">
-        <v>1815600</v>
+        <v>1852700</v>
       </c>
       <c r="J46" s="3">
-        <v>1417300</v>
+        <v>1446300</v>
       </c>
       <c r="K46" s="3">
         <v>1026300</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>64200</v>
+        <v>65500</v>
       </c>
       <c r="E47" s="3">
-        <v>59200</v>
+        <v>60400</v>
       </c>
       <c r="F47" s="3">
-        <v>10800</v>
+        <v>11000</v>
       </c>
       <c r="G47" s="3">
-        <v>12200</v>
+        <v>12500</v>
       </c>
       <c r="H47" s="3">
-        <v>10500</v>
+        <v>10700</v>
       </c>
       <c r="I47" s="3">
-        <v>10100</v>
+        <v>10300</v>
       </c>
       <c r="J47" s="3">
-        <v>22000</v>
+        <v>22400</v>
       </c>
       <c r="K47" s="3">
         <v>18700</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>55300</v>
+        <v>56400</v>
       </c>
       <c r="E48" s="3">
+        <v>52200</v>
+      </c>
+      <c r="F48" s="3">
+        <v>72600</v>
+      </c>
+      <c r="G48" s="3">
+        <v>87300</v>
+      </c>
+      <c r="H48" s="3">
         <v>51200</v>
       </c>
-      <c r="F48" s="3">
-        <v>71100</v>
-      </c>
-      <c r="G48" s="3">
-        <v>85600</v>
-      </c>
-      <c r="H48" s="3">
-        <v>50100</v>
-      </c>
       <c r="I48" s="3">
-        <v>23500</v>
+        <v>24000</v>
       </c>
       <c r="J48" s="3">
-        <v>18000</v>
+        <v>18400</v>
       </c>
       <c r="K48" s="3">
         <v>37200</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>572500</v>
+        <v>584200</v>
       </c>
       <c r="E49" s="3">
-        <v>583100</v>
+        <v>595000</v>
       </c>
       <c r="F49" s="3">
-        <v>594000</v>
+        <v>606100</v>
       </c>
       <c r="G49" s="3">
-        <v>623400</v>
+        <v>636100</v>
       </c>
       <c r="H49" s="3">
-        <v>211700</v>
+        <v>216000</v>
       </c>
       <c r="I49" s="3">
-        <v>213300</v>
+        <v>217600</v>
       </c>
       <c r="J49" s="3">
-        <v>214900</v>
+        <v>219300</v>
       </c>
       <c r="K49" s="3">
         <v>423600</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>41800</v>
+        <v>42600</v>
       </c>
       <c r="E52" s="3">
-        <v>37500</v>
+        <v>38300</v>
       </c>
       <c r="F52" s="3">
-        <v>25100</v>
+        <v>25600</v>
       </c>
       <c r="G52" s="3">
-        <v>20300</v>
+        <v>20700</v>
       </c>
       <c r="H52" s="3">
-        <v>114200</v>
+        <v>116500</v>
       </c>
       <c r="I52" s="3">
-        <v>114400</v>
+        <v>116700</v>
       </c>
       <c r="J52" s="3">
-        <v>26500</v>
+        <v>27100</v>
       </c>
       <c r="K52" s="3">
         <v>21600</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>4260300</v>
+        <v>4347200</v>
       </c>
       <c r="E54" s="3">
-        <v>4105500</v>
+        <v>4189300</v>
       </c>
       <c r="F54" s="3">
-        <v>3923700</v>
+        <v>4003800</v>
       </c>
       <c r="G54" s="3">
-        <v>3278700</v>
+        <v>3345600</v>
       </c>
       <c r="H54" s="3">
-        <v>2646600</v>
+        <v>2700600</v>
       </c>
       <c r="I54" s="3">
-        <v>2176900</v>
+        <v>2221300</v>
       </c>
       <c r="J54" s="3">
-        <v>1698700</v>
+        <v>1733300</v>
       </c>
       <c r="K54" s="3">
         <v>1296900</v>
@@ -2661,22 +2661,22 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="E57" s="3">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="F57" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="G57" s="3">
-        <v>11000</v>
+        <v>11300</v>
       </c>
       <c r="H57" s="3">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="I57" s="3">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="J57" s="3">
         <v>1400</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>697800</v>
+        <v>712100</v>
       </c>
       <c r="E59" s="3">
-        <v>557000</v>
+        <v>568400</v>
       </c>
       <c r="F59" s="3">
-        <v>546300</v>
+        <v>557500</v>
       </c>
       <c r="G59" s="3">
-        <v>567300</v>
+        <v>578800</v>
       </c>
       <c r="H59" s="3">
-        <v>542900</v>
+        <v>554000</v>
       </c>
       <c r="I59" s="3">
-        <v>572700</v>
+        <v>584300</v>
       </c>
       <c r="J59" s="3">
-        <v>535900</v>
+        <v>546900</v>
       </c>
       <c r="K59" s="3">
         <v>503700</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>701200</v>
+        <v>715500</v>
       </c>
       <c r="E60" s="3">
-        <v>560700</v>
+        <v>572200</v>
       </c>
       <c r="F60" s="3">
-        <v>550700</v>
+        <v>562000</v>
       </c>
       <c r="G60" s="3">
-        <v>578300</v>
+        <v>590100</v>
       </c>
       <c r="H60" s="3">
-        <v>547900</v>
+        <v>559100</v>
       </c>
       <c r="I60" s="3">
-        <v>575400</v>
+        <v>587100</v>
       </c>
       <c r="J60" s="3">
-        <v>537300</v>
+        <v>548300</v>
       </c>
       <c r="K60" s="3">
         <v>351300</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>81100</v>
+        <v>82800</v>
       </c>
       <c r="E62" s="3">
-        <v>78500</v>
+        <v>80100</v>
       </c>
       <c r="F62" s="3">
-        <v>83600</v>
+        <v>85400</v>
       </c>
       <c r="G62" s="3">
-        <v>101700</v>
+        <v>103800</v>
       </c>
       <c r="H62" s="3">
-        <v>80700</v>
+        <v>82300</v>
       </c>
       <c r="I62" s="3">
+        <v>67700</v>
+      </c>
+      <c r="J62" s="3">
         <v>66300</v>
-      </c>
-      <c r="J62" s="3">
-        <v>65000</v>
       </c>
       <c r="K62" s="3">
         <v>68600</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>954300</v>
+        <v>973800</v>
       </c>
       <c r="E66" s="3">
-        <v>805100</v>
+        <v>821500</v>
       </c>
       <c r="F66" s="3">
-        <v>797800</v>
+        <v>814100</v>
       </c>
       <c r="G66" s="3">
-        <v>843500</v>
+        <v>860700</v>
       </c>
       <c r="H66" s="3">
-        <v>625400</v>
+        <v>638200</v>
       </c>
       <c r="I66" s="3">
-        <v>638400</v>
+        <v>651500</v>
       </c>
       <c r="J66" s="3">
-        <v>600100</v>
+        <v>612300</v>
       </c>
       <c r="K66" s="3">
         <v>418600</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2293700</v>
+        <v>2340500</v>
       </c>
       <c r="E72" s="3">
-        <v>2237700</v>
+        <v>2283400</v>
       </c>
       <c r="F72" s="3">
-        <v>2046300</v>
+        <v>2088100</v>
       </c>
       <c r="G72" s="3">
-        <v>1860400</v>
+        <v>1898400</v>
       </c>
       <c r="H72" s="3">
-        <v>1478100</v>
+        <v>1508200</v>
       </c>
       <c r="I72" s="3">
-        <v>1036000</v>
+        <v>1057100</v>
       </c>
       <c r="J72" s="3">
-        <v>639300</v>
+        <v>652400</v>
       </c>
       <c r="K72" s="3">
         <v>444800</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3305900</v>
+        <v>3373400</v>
       </c>
       <c r="E76" s="3">
-        <v>3300500</v>
+        <v>3367800</v>
       </c>
       <c r="F76" s="3">
-        <v>3125800</v>
+        <v>3189700</v>
       </c>
       <c r="G76" s="3">
-        <v>2435200</v>
+        <v>2484900</v>
       </c>
       <c r="H76" s="3">
-        <v>2021200</v>
+        <v>2062400</v>
       </c>
       <c r="I76" s="3">
-        <v>1538500</v>
+        <v>1569900</v>
       </c>
       <c r="J76" s="3">
-        <v>1098600</v>
+        <v>1121000</v>
       </c>
       <c r="K76" s="3">
         <v>878200</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>259800</v>
+        <v>265100</v>
       </c>
       <c r="E81" s="3">
-        <v>249700</v>
+        <v>254800</v>
       </c>
       <c r="F81" s="3">
-        <v>296800</v>
+        <v>302900</v>
       </c>
       <c r="G81" s="3">
-        <v>470500</v>
+        <v>480100</v>
       </c>
       <c r="H81" s="3">
-        <v>442100</v>
+        <v>451100</v>
       </c>
       <c r="I81" s="3">
-        <v>396700</v>
+        <v>404800</v>
       </c>
       <c r="J81" s="3">
-        <v>276500</v>
+        <v>282200</v>
       </c>
       <c r="K81" s="3">
         <v>169600</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>33800</v>
+        <v>34500</v>
       </c>
       <c r="E83" s="3">
-        <v>42200</v>
+        <v>43000</v>
       </c>
       <c r="F83" s="3">
-        <v>42700</v>
+        <v>43600</v>
       </c>
       <c r="G83" s="3">
-        <v>23500</v>
+        <v>24000</v>
       </c>
       <c r="H83" s="3">
-        <v>16400</v>
+        <v>16700</v>
       </c>
       <c r="I83" s="3">
-        <v>14100</v>
+        <v>14400</v>
       </c>
       <c r="J83" s="3">
-        <v>12300</v>
+        <v>12500</v>
       </c>
       <c r="K83" s="3">
         <v>9600</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>338700</v>
+        <v>345600</v>
       </c>
       <c r="E89" s="3">
-        <v>354400</v>
+        <v>361600</v>
       </c>
       <c r="F89" s="3">
-        <v>486900</v>
+        <v>496800</v>
       </c>
       <c r="G89" s="3">
-        <v>459500</v>
+        <v>468800</v>
       </c>
       <c r="H89" s="3">
-        <v>399200</v>
+        <v>407300</v>
       </c>
       <c r="I89" s="3">
-        <v>429900</v>
+        <v>438700</v>
       </c>
       <c r="J89" s="3">
-        <v>340400</v>
+        <v>347300</v>
       </c>
       <c r="K89" s="3">
         <v>217400</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-10900</v>
+        <v>-11100</v>
       </c>
       <c r="E91" s="3">
-        <v>-16100</v>
+        <v>-16400</v>
       </c>
       <c r="F91" s="3">
-        <v>-30200</v>
+        <v>-30800</v>
       </c>
       <c r="G91" s="3">
-        <v>-36500</v>
+        <v>-37200</v>
       </c>
       <c r="H91" s="3">
-        <v>-28200</v>
+        <v>-28800</v>
       </c>
       <c r="I91" s="3">
-        <v>-15700</v>
+        <v>-16000</v>
       </c>
       <c r="J91" s="3">
-        <v>-11900</v>
+        <v>-12200</v>
       </c>
       <c r="K91" s="3">
         <v>-12300</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>138200</v>
+        <v>141000</v>
       </c>
       <c r="E94" s="3">
-        <v>-429600</v>
+        <v>-438400</v>
       </c>
       <c r="F94" s="3">
-        <v>-526800</v>
+        <v>-537600</v>
       </c>
       <c r="G94" s="3">
-        <v>-412500</v>
+        <v>-420900</v>
       </c>
       <c r="H94" s="3">
-        <v>-161400</v>
+        <v>-164700</v>
       </c>
       <c r="I94" s="3">
-        <v>-456100</v>
+        <v>-465400</v>
       </c>
       <c r="J94" s="3">
-        <v>-678900</v>
+        <v>-692800</v>
       </c>
       <c r="K94" s="3">
         <v>-71100</v>
@@ -4227,22 +4227,22 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-67800</v>
+        <v>-69200</v>
       </c>
       <c r="E96" s="3">
-        <v>-58300</v>
+        <v>-59400</v>
       </c>
       <c r="F96" s="3">
-        <v>-93000</v>
+        <v>-94900</v>
       </c>
       <c r="G96" s="3">
-        <v>-90000</v>
+        <v>-91800</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-82300</v>
+        <v>-84000</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-155400</v>
+        <v>-158500</v>
       </c>
       <c r="E100" s="3">
-        <v>-157500</v>
+        <v>-160700</v>
       </c>
       <c r="F100" s="3">
-        <v>400400</v>
+        <v>408600</v>
       </c>
       <c r="G100" s="3">
-        <v>-75600</v>
+        <v>-77100</v>
       </c>
       <c r="H100" s="3">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="I100" s="3">
-        <v>-75200</v>
+        <v>-76700</v>
       </c>
       <c r="J100" s="3">
-        <v>8400</v>
+        <v>8600</v>
       </c>
       <c r="K100" s="3">
         <v>3900</v>
@@ -4452,22 +4452,22 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-2000</v>
+        <v>-2100</v>
       </c>
       <c r="E101" s="3">
-        <v>23300</v>
+        <v>23700</v>
       </c>
       <c r="F101" s="3">
-        <v>-6500</v>
+        <v>-6600</v>
       </c>
       <c r="G101" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="H101" s="3">
-        <v>-1800</v>
+        <v>-1900</v>
       </c>
       <c r="I101" s="3">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="J101" s="3">
         <v>-400</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>319500</v>
+        <v>326000</v>
       </c>
       <c r="E102" s="3">
-        <v>-209500</v>
+        <v>-213700</v>
       </c>
       <c r="F102" s="3">
-        <v>354000</v>
+        <v>361200</v>
       </c>
       <c r="G102" s="3">
-        <v>-31000</v>
+        <v>-31600</v>
       </c>
       <c r="H102" s="3">
-        <v>245400</v>
+        <v>250500</v>
       </c>
       <c r="I102" s="3">
-        <v>-96000</v>
+        <v>-97900</v>
       </c>
       <c r="J102" s="3">
-        <v>-330400</v>
+        <v>-337200</v>
       </c>
       <c r="K102" s="3">
         <v>150400</v>

--- a/AAII_Financials/Yearly/ATHM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ATHM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>ATHM</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1012800</v>
+        <v>1013100</v>
       </c>
       <c r="E8" s="3">
-        <v>978500</v>
+        <v>1006300</v>
       </c>
       <c r="F8" s="3">
-        <v>1020300</v>
+        <v>1139200</v>
       </c>
       <c r="G8" s="3">
-        <v>1220700</v>
+        <v>1326300</v>
       </c>
       <c r="H8" s="3">
-        <v>1187200</v>
+        <v>1209400</v>
       </c>
       <c r="I8" s="3">
-        <v>1019700</v>
+        <v>1051700</v>
       </c>
       <c r="J8" s="3">
-        <v>875500</v>
+        <v>954400</v>
       </c>
       <c r="K8" s="3">
         <v>823200</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>185600</v>
+        <v>185700</v>
       </c>
       <c r="E9" s="3">
-        <v>160400</v>
+        <v>165000</v>
       </c>
       <c r="F9" s="3">
-        <v>142200</v>
+        <v>158800</v>
       </c>
       <c r="G9" s="3">
-        <v>121800</v>
+        <v>132400</v>
       </c>
       <c r="H9" s="3">
-        <v>108600</v>
+        <v>110600</v>
       </c>
       <c r="I9" s="3">
-        <v>82900</v>
+        <v>85500</v>
       </c>
       <c r="J9" s="3">
-        <v>123200</v>
+        <v>134300</v>
       </c>
       <c r="K9" s="3">
         <v>282200</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>827200</v>
+        <v>827500</v>
       </c>
       <c r="E10" s="3">
-        <v>818100</v>
+        <v>841400</v>
       </c>
       <c r="F10" s="3">
-        <v>878100</v>
+        <v>980400</v>
       </c>
       <c r="G10" s="3">
-        <v>1098800</v>
+        <v>1193900</v>
       </c>
       <c r="H10" s="3">
-        <v>1078600</v>
+        <v>1098700</v>
       </c>
       <c r="I10" s="3">
-        <v>936800</v>
+        <v>966100</v>
       </c>
       <c r="J10" s="3">
-        <v>752300</v>
+        <v>820100</v>
       </c>
       <c r="K10" s="3">
         <v>541000</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>190100</v>
+        <v>190200</v>
       </c>
       <c r="E12" s="3">
-        <v>199800</v>
+        <v>205500</v>
       </c>
       <c r="F12" s="3">
-        <v>197100</v>
+        <v>220100</v>
       </c>
       <c r="G12" s="3">
-        <v>192300</v>
+        <v>209000</v>
       </c>
       <c r="H12" s="3">
-        <v>182000</v>
+        <v>185400</v>
       </c>
       <c r="I12" s="3">
-        <v>160000</v>
+        <v>165100</v>
       </c>
       <c r="J12" s="3">
-        <v>123900</v>
+        <v>135100</v>
       </c>
       <c r="K12" s="3">
         <v>78900</v>
@@ -969,14 +969,14 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="E14" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-7300</v>
+      <c r="D14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>17</v>
@@ -984,8 +984,8 @@
       <c r="H14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>17</v>
+      <c r="I14" s="3">
+        <v>1600</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>17</v>
@@ -1015,25 +1015,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>34500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>44200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>48600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>26100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>14800</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>13700</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>885900</v>
+        <v>852700</v>
       </c>
       <c r="E17" s="3">
-        <v>840900</v>
+        <v>825500</v>
       </c>
       <c r="F17" s="3">
-        <v>803300</v>
+        <v>858800</v>
       </c>
       <c r="G17" s="3">
-        <v>839400</v>
+        <v>844100</v>
       </c>
       <c r="H17" s="3">
-        <v>798300</v>
+        <v>744700</v>
       </c>
       <c r="I17" s="3">
-        <v>663400</v>
+        <v>634500</v>
       </c>
       <c r="J17" s="3">
-        <v>587500</v>
+        <v>639100</v>
       </c>
       <c r="K17" s="3">
         <v>663900</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>127000</v>
+        <v>160400</v>
       </c>
       <c r="E18" s="3">
-        <v>137700</v>
+        <v>180900</v>
       </c>
       <c r="F18" s="3">
-        <v>217000</v>
+        <v>280500</v>
       </c>
       <c r="G18" s="3">
-        <v>381300</v>
+        <v>482200</v>
       </c>
       <c r="H18" s="3">
-        <v>388800</v>
+        <v>464700</v>
       </c>
       <c r="I18" s="3">
-        <v>356300</v>
+        <v>417100</v>
       </c>
       <c r="J18" s="3">
-        <v>288100</v>
+        <v>315300</v>
       </c>
       <c r="K18" s="3">
         <v>159300</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>154700</v>
+        <v>-4100</v>
       </c>
       <c r="E20" s="3">
-        <v>110900</v>
+        <v>7200</v>
       </c>
       <c r="F20" s="3">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>135900</v>
+        <v>200</v>
       </c>
       <c r="H20" s="3">
-        <v>132900</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>100600</v>
+        <v>-3600</v>
       </c>
       <c r="J20" s="3">
-        <v>30800</v>
+        <v>1600</v>
       </c>
       <c r="K20" s="3">
         <v>13200</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>316000</v>
+        <v>199000</v>
       </c>
       <c r="E21" s="3">
-        <v>291400</v>
+        <v>217900</v>
       </c>
       <c r="F21" s="3">
-        <v>350400</v>
+        <v>329100</v>
       </c>
       <c r="G21" s="3">
-        <v>541100</v>
+        <v>508100</v>
       </c>
       <c r="H21" s="3">
-        <v>538400</v>
+        <v>481900</v>
       </c>
       <c r="I21" s="3">
-        <v>471300</v>
+        <v>435500</v>
       </c>
       <c r="J21" s="3">
-        <v>331300</v>
+        <v>327400</v>
       </c>
       <c r="K21" s="3">
         <v>182100</v>
@@ -1274,26 +1274,26 @@
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>281600</v>
+        <v>281700</v>
       </c>
       <c r="E23" s="3">
-        <v>248500</v>
+        <v>255600</v>
       </c>
       <c r="F23" s="3">
-        <v>306900</v>
+        <v>342700</v>
       </c>
       <c r="G23" s="3">
-        <v>517200</v>
+        <v>542100</v>
       </c>
       <c r="H23" s="3">
-        <v>521800</v>
+        <v>531500</v>
       </c>
       <c r="I23" s="3">
-        <v>457000</v>
+        <v>471300</v>
       </c>
       <c r="J23" s="3">
-        <v>318800</v>
+        <v>347600</v>
       </c>
       <c r="K23" s="3">
         <v>172400</v>
@@ -1368,22 +1368,22 @@
         <v>10200</v>
       </c>
       <c r="E24" s="3">
-        <v>-8700</v>
+        <v>-9000</v>
       </c>
       <c r="F24" s="3">
-        <v>4800</v>
+        <v>5400</v>
       </c>
       <c r="G24" s="3">
-        <v>36800</v>
+        <v>40000</v>
       </c>
       <c r="H24" s="3">
-        <v>70500</v>
+        <v>71900</v>
       </c>
       <c r="I24" s="3">
-        <v>53300</v>
+        <v>54900</v>
       </c>
       <c r="J24" s="3">
-        <v>37700</v>
+        <v>41000</v>
       </c>
       <c r="K24" s="3">
         <v>4500</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>271400</v>
+        <v>271500</v>
       </c>
       <c r="E26" s="3">
-        <v>257200</v>
+        <v>264500</v>
       </c>
       <c r="F26" s="3">
-        <v>302100</v>
+        <v>337400</v>
       </c>
       <c r="G26" s="3">
-        <v>480400</v>
+        <v>502100</v>
       </c>
       <c r="H26" s="3">
-        <v>451200</v>
+        <v>459700</v>
       </c>
       <c r="I26" s="3">
-        <v>403700</v>
+        <v>416400</v>
       </c>
       <c r="J26" s="3">
-        <v>281200</v>
+        <v>306500</v>
       </c>
       <c r="K26" s="3">
         <v>167900</v>
@@ -1503,22 +1503,22 @@
         <v>265100</v>
       </c>
       <c r="E27" s="3">
-        <v>254800</v>
+        <v>262000</v>
       </c>
       <c r="F27" s="3">
-        <v>302900</v>
+        <v>338200</v>
       </c>
       <c r="G27" s="3">
-        <v>480100</v>
+        <v>501700</v>
       </c>
       <c r="H27" s="3">
-        <v>451100</v>
+        <v>459600</v>
       </c>
       <c r="I27" s="3">
-        <v>404800</v>
+        <v>417400</v>
       </c>
       <c r="J27" s="3">
-        <v>282200</v>
+        <v>307600</v>
       </c>
       <c r="K27" s="3">
         <v>169600</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-154700</v>
+        <v>4100</v>
       </c>
       <c r="E32" s="3">
-        <v>-110900</v>
+        <v>-7200</v>
       </c>
       <c r="F32" s="3">
-        <v>-90000</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-135900</v>
+        <v>-200</v>
       </c>
       <c r="H32" s="3">
-        <v>-132900</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>-100600</v>
+        <v>3600</v>
       </c>
       <c r="J32" s="3">
-        <v>-30800</v>
+        <v>-1600</v>
       </c>
       <c r="K32" s="3">
         <v>-13200</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>265100</v>
+        <v>272900</v>
       </c>
       <c r="E33" s="3">
-        <v>254800</v>
+        <v>269000</v>
       </c>
       <c r="F33" s="3">
-        <v>302900</v>
+        <v>354000</v>
       </c>
       <c r="G33" s="3">
-        <v>480100</v>
+        <v>501700</v>
       </c>
       <c r="H33" s="3">
-        <v>451100</v>
+        <v>459600</v>
       </c>
       <c r="I33" s="3">
-        <v>404800</v>
+        <v>417400</v>
       </c>
       <c r="J33" s="3">
-        <v>282200</v>
+        <v>307600</v>
       </c>
       <c r="K33" s="3">
         <v>169600</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>265100</v>
+        <v>272900</v>
       </c>
       <c r="E35" s="3">
-        <v>254800</v>
+        <v>269000</v>
       </c>
       <c r="F35" s="3">
-        <v>302900</v>
+        <v>354000</v>
       </c>
       <c r="G35" s="3">
-        <v>480100</v>
+        <v>501700</v>
       </c>
       <c r="H35" s="3">
-        <v>451100</v>
+        <v>459600</v>
       </c>
       <c r="I35" s="3">
-        <v>404800</v>
+        <v>417400</v>
       </c>
       <c r="J35" s="3">
-        <v>282200</v>
+        <v>307600</v>
       </c>
       <c r="K35" s="3">
         <v>169600</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>704400</v>
+        <v>704600</v>
       </c>
       <c r="E41" s="3">
-        <v>394900</v>
+        <v>406200</v>
       </c>
       <c r="F41" s="3">
-        <v>597300</v>
+        <v>666900</v>
       </c>
       <c r="G41" s="3">
-        <v>246900</v>
+        <v>268200</v>
       </c>
       <c r="H41" s="3">
-        <v>280300</v>
+        <v>285600</v>
       </c>
       <c r="I41" s="3">
-        <v>29900</v>
+        <v>30800</v>
       </c>
       <c r="J41" s="3">
-        <v>128500</v>
+        <v>140100</v>
       </c>
       <c r="K41" s="3">
         <v>454800</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2617500</v>
+        <v>2616400</v>
       </c>
       <c r="E42" s="3">
-        <v>2720900</v>
+        <v>2795300</v>
       </c>
       <c r="F42" s="3">
-        <v>2328500</v>
+        <v>2596800</v>
       </c>
       <c r="G42" s="3">
-        <v>1817100</v>
+        <v>1972600</v>
       </c>
       <c r="H42" s="3">
-        <v>1526300</v>
+        <v>1552100</v>
       </c>
       <c r="I42" s="3">
-        <v>1389500</v>
+        <v>1432100</v>
       </c>
       <c r="J42" s="3">
-        <v>1022700</v>
+        <v>1113100</v>
       </c>
       <c r="K42" s="3">
         <v>335800</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>215700</v>
+        <v>215800</v>
       </c>
       <c r="E43" s="3">
-        <v>284600</v>
+        <v>292200</v>
       </c>
       <c r="F43" s="3">
-        <v>319300</v>
+        <v>356600</v>
       </c>
       <c r="G43" s="3">
-        <v>447100</v>
+        <v>524200</v>
       </c>
       <c r="H43" s="3">
-        <v>459700</v>
+        <v>477300</v>
       </c>
       <c r="I43" s="3">
-        <v>399000</v>
+        <v>418600</v>
       </c>
       <c r="J43" s="3">
-        <v>270400</v>
+        <v>299200</v>
       </c>
       <c r="K43" s="3">
         <v>342900</v>
@@ -2127,26 +2127,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K44" s="3">
         <v>13200</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>60900</v>
+        <v>41700</v>
       </c>
       <c r="E45" s="3">
         <v>43000</v>
       </c>
       <c r="F45" s="3">
-        <v>43400</v>
+        <v>37500</v>
       </c>
       <c r="G45" s="3">
-        <v>77900</v>
+        <v>47800</v>
       </c>
       <c r="H45" s="3">
-        <v>39900</v>
+        <v>34500</v>
       </c>
       <c r="I45" s="3">
-        <v>34300</v>
+        <v>29200</v>
       </c>
       <c r="J45" s="3">
-        <v>24600</v>
+        <v>24200</v>
       </c>
       <c r="K45" s="3">
         <v>111900</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3598500</v>
+        <v>3599700</v>
       </c>
       <c r="E46" s="3">
-        <v>3443400</v>
+        <v>3541300</v>
       </c>
       <c r="F46" s="3">
-        <v>3288500</v>
+        <v>3671800</v>
       </c>
       <c r="G46" s="3">
-        <v>2589000</v>
+        <v>2812900</v>
       </c>
       <c r="H46" s="3">
-        <v>2306200</v>
+        <v>2349400</v>
       </c>
       <c r="I46" s="3">
-        <v>1852700</v>
+        <v>1910700</v>
       </c>
       <c r="J46" s="3">
-        <v>1446300</v>
+        <v>1576600</v>
       </c>
       <c r="K46" s="3">
         <v>1026300</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>65500</v>
+        <v>63200</v>
       </c>
       <c r="E47" s="3">
-        <v>60400</v>
+        <v>60800</v>
       </c>
       <c r="F47" s="3">
-        <v>11000</v>
+        <v>11100</v>
       </c>
       <c r="G47" s="3">
-        <v>12500</v>
+        <v>10800</v>
       </c>
       <c r="H47" s="3">
-        <v>10700</v>
+        <v>119100</v>
       </c>
       <c r="I47" s="3">
-        <v>10300</v>
+        <v>108500</v>
       </c>
       <c r="J47" s="3">
-        <v>22400</v>
+        <v>22700</v>
       </c>
       <c r="K47" s="3">
         <v>18700</v>
@@ -2311,22 +2311,22 @@
         <v>56400</v>
       </c>
       <c r="E48" s="3">
-        <v>52200</v>
+        <v>53700</v>
       </c>
       <c r="F48" s="3">
-        <v>72600</v>
+        <v>81100</v>
       </c>
       <c r="G48" s="3">
-        <v>87300</v>
+        <v>94900</v>
       </c>
       <c r="H48" s="3">
-        <v>51200</v>
+        <v>52100</v>
       </c>
       <c r="I48" s="3">
-        <v>24000</v>
+        <v>24700</v>
       </c>
       <c r="J48" s="3">
-        <v>18400</v>
+        <v>20000</v>
       </c>
       <c r="K48" s="3">
         <v>37200</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>584200</v>
+        <v>584400</v>
       </c>
       <c r="E49" s="3">
-        <v>595000</v>
+        <v>611900</v>
       </c>
       <c r="F49" s="3">
-        <v>606100</v>
+        <v>676800</v>
       </c>
       <c r="G49" s="3">
-        <v>636100</v>
+        <v>691100</v>
       </c>
       <c r="H49" s="3">
-        <v>216000</v>
+        <v>220000</v>
       </c>
       <c r="I49" s="3">
-        <v>217600</v>
+        <v>224400</v>
       </c>
       <c r="J49" s="3">
-        <v>219300</v>
+        <v>239000</v>
       </c>
       <c r="K49" s="3">
         <v>423600</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>42600</v>
+        <v>3200</v>
       </c>
       <c r="E52" s="3">
-        <v>38300</v>
+        <v>2200</v>
       </c>
       <c r="F52" s="3">
-        <v>25600</v>
+        <v>2000</v>
       </c>
       <c r="G52" s="3">
-        <v>20700</v>
+        <v>13100</v>
       </c>
       <c r="H52" s="3">
-        <v>116500</v>
+        <v>6500</v>
       </c>
       <c r="I52" s="3">
-        <v>116700</v>
+        <v>9400</v>
       </c>
       <c r="J52" s="3">
-        <v>27100</v>
+        <v>4400</v>
       </c>
       <c r="K52" s="3">
         <v>21600</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>4347200</v>
+        <v>4348600</v>
       </c>
       <c r="E54" s="3">
-        <v>4189300</v>
+        <v>4308400</v>
       </c>
       <c r="F54" s="3">
-        <v>4003800</v>
+        <v>4470500</v>
       </c>
       <c r="G54" s="3">
-        <v>3345600</v>
+        <v>3634900</v>
       </c>
       <c r="H54" s="3">
-        <v>2700600</v>
+        <v>2751100</v>
       </c>
       <c r="I54" s="3">
-        <v>2221300</v>
+        <v>2290900</v>
       </c>
       <c r="J54" s="3">
-        <v>1733300</v>
+        <v>1889600</v>
       </c>
       <c r="K54" s="3">
         <v>1296900</v>
@@ -2660,26 +2660,26 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>3500</v>
-      </c>
-      <c r="E57" s="3">
-        <v>3800</v>
-      </c>
-      <c r="F57" s="3">
-        <v>4500</v>
-      </c>
-      <c r="G57" s="3">
-        <v>11300</v>
-      </c>
-      <c r="H57" s="3">
-        <v>5100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>2800</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1400</v>
+      <c r="D57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K57" s="3">
         <v>2300</v>
@@ -2706,19 +2706,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>15100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>15100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>17200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>712100</v>
+        <v>317800</v>
       </c>
       <c r="E59" s="3">
-        <v>568400</v>
+        <v>231600</v>
       </c>
       <c r="F59" s="3">
-        <v>557500</v>
+        <v>332100</v>
       </c>
       <c r="G59" s="3">
-        <v>578800</v>
+        <v>284100</v>
       </c>
       <c r="H59" s="3">
-        <v>554000</v>
+        <v>243000</v>
       </c>
       <c r="I59" s="3">
-        <v>584300</v>
+        <v>278300</v>
       </c>
       <c r="J59" s="3">
-        <v>546900</v>
+        <v>369400</v>
       </c>
       <c r="K59" s="3">
         <v>503700</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>715500</v>
+        <v>715800</v>
       </c>
       <c r="E60" s="3">
-        <v>572200</v>
+        <v>588500</v>
       </c>
       <c r="F60" s="3">
-        <v>562000</v>
+        <v>627500</v>
       </c>
       <c r="G60" s="3">
-        <v>590100</v>
+        <v>641100</v>
       </c>
       <c r="H60" s="3">
-        <v>559100</v>
+        <v>569600</v>
       </c>
       <c r="I60" s="3">
-        <v>587100</v>
+        <v>605500</v>
       </c>
       <c r="J60" s="3">
-        <v>548300</v>
+        <v>597700</v>
       </c>
       <c r="K60" s="3">
         <v>351300</v>
@@ -2841,19 +2841,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>12600</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>13900</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2885,26 +2885,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>82800</v>
-      </c>
-      <c r="E62" s="3">
-        <v>80100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>85400</v>
+      <c r="D62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G62" s="3">
-        <v>103800</v>
+        <v>2200</v>
       </c>
       <c r="H62" s="3">
-        <v>82300</v>
+        <v>3200</v>
       </c>
       <c r="I62" s="3">
-        <v>67700</v>
+        <v>3500</v>
       </c>
       <c r="J62" s="3">
-        <v>66300</v>
+        <v>4900</v>
       </c>
       <c r="K62" s="3">
         <v>68600</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>973800</v>
+        <v>798600</v>
       </c>
       <c r="E66" s="3">
-        <v>821500</v>
+        <v>670900</v>
       </c>
       <c r="F66" s="3">
-        <v>814100</v>
+        <v>722800</v>
       </c>
       <c r="G66" s="3">
-        <v>860700</v>
+        <v>753900</v>
       </c>
       <c r="H66" s="3">
-        <v>638200</v>
+        <v>653500</v>
       </c>
       <c r="I66" s="3">
-        <v>651500</v>
+        <v>675300</v>
       </c>
       <c r="J66" s="3">
-        <v>612300</v>
+        <v>670000</v>
       </c>
       <c r="K66" s="3">
         <v>418600</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2340500</v>
+        <v>2341200</v>
       </c>
       <c r="E72" s="3">
-        <v>2283400</v>
+        <v>2348300</v>
       </c>
       <c r="F72" s="3">
-        <v>2088100</v>
+        <v>2331500</v>
       </c>
       <c r="G72" s="3">
-        <v>1898400</v>
+        <v>2062600</v>
       </c>
       <c r="H72" s="3">
-        <v>1508200</v>
+        <v>1536500</v>
       </c>
       <c r="I72" s="3">
-        <v>1057100</v>
+        <v>1090200</v>
       </c>
       <c r="J72" s="3">
-        <v>652400</v>
+        <v>711200</v>
       </c>
       <c r="K72" s="3">
         <v>444800</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3373400</v>
+        <v>3374500</v>
       </c>
       <c r="E76" s="3">
-        <v>3367800</v>
+        <v>3463600</v>
       </c>
       <c r="F76" s="3">
-        <v>3189700</v>
+        <v>3561500</v>
       </c>
       <c r="G76" s="3">
-        <v>2484900</v>
+        <v>2699800</v>
       </c>
       <c r="H76" s="3">
-        <v>2062400</v>
+        <v>2101000</v>
       </c>
       <c r="I76" s="3">
-        <v>1569900</v>
+        <v>1619000</v>
       </c>
       <c r="J76" s="3">
-        <v>1121000</v>
+        <v>1222100</v>
       </c>
       <c r="K76" s="3">
         <v>878200</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>265100</v>
+        <v>272900</v>
       </c>
       <c r="E81" s="3">
-        <v>254800</v>
+        <v>269000</v>
       </c>
       <c r="F81" s="3">
-        <v>302900</v>
+        <v>354000</v>
       </c>
       <c r="G81" s="3">
-        <v>480100</v>
+        <v>501700</v>
       </c>
       <c r="H81" s="3">
-        <v>451100</v>
+        <v>459600</v>
       </c>
       <c r="I81" s="3">
-        <v>404800</v>
+        <v>417400</v>
       </c>
       <c r="J81" s="3">
-        <v>282200</v>
+        <v>307600</v>
       </c>
       <c r="K81" s="3">
         <v>169600</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>34500</v>
+        <v>38900</v>
       </c>
       <c r="E83" s="3">
-        <v>43000</v>
+        <v>50000</v>
       </c>
       <c r="F83" s="3">
-        <v>43600</v>
+        <v>54700</v>
       </c>
       <c r="G83" s="3">
-        <v>24000</v>
+        <v>40900</v>
       </c>
       <c r="H83" s="3">
-        <v>16700</v>
+        <v>32900</v>
       </c>
       <c r="I83" s="3">
-        <v>14400</v>
+        <v>13100</v>
       </c>
       <c r="J83" s="3">
-        <v>12500</v>
+        <v>12600</v>
       </c>
       <c r="K83" s="3">
         <v>9600</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>345600</v>
+        <v>345700</v>
       </c>
       <c r="E89" s="3">
-        <v>361600</v>
+        <v>371900</v>
       </c>
       <c r="F89" s="3">
-        <v>496800</v>
+        <v>554700</v>
       </c>
       <c r="G89" s="3">
-        <v>468800</v>
+        <v>509400</v>
       </c>
       <c r="H89" s="3">
-        <v>407300</v>
+        <v>415000</v>
       </c>
       <c r="I89" s="3">
-        <v>438700</v>
+        <v>452400</v>
       </c>
       <c r="J89" s="3">
-        <v>347300</v>
+        <v>378600</v>
       </c>
       <c r="K89" s="3">
         <v>217400</v>
@@ -4031,22 +4031,22 @@
         <v>-11100</v>
       </c>
       <c r="E91" s="3">
-        <v>-16400</v>
+        <v>-16900</v>
       </c>
       <c r="F91" s="3">
-        <v>-30800</v>
+        <v>-34400</v>
       </c>
       <c r="G91" s="3">
-        <v>-37200</v>
+        <v>-40400</v>
       </c>
       <c r="H91" s="3">
-        <v>-28800</v>
+        <v>-29300</v>
       </c>
       <c r="I91" s="3">
-        <v>-16000</v>
+        <v>-16500</v>
       </c>
       <c r="J91" s="3">
-        <v>-12200</v>
+        <v>-13300</v>
       </c>
       <c r="K91" s="3">
         <v>-12300</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>141000</v>
+        <v>141100</v>
       </c>
       <c r="E94" s="3">
-        <v>-438400</v>
+        <v>-450800</v>
       </c>
       <c r="F94" s="3">
-        <v>-537600</v>
+        <v>-600200</v>
       </c>
       <c r="G94" s="3">
-        <v>-420900</v>
+        <v>-457300</v>
       </c>
       <c r="H94" s="3">
-        <v>-164700</v>
+        <v>-167800</v>
       </c>
       <c r="I94" s="3">
-        <v>-465400</v>
+        <v>-480000</v>
       </c>
       <c r="J94" s="3">
-        <v>-692800</v>
+        <v>-755200</v>
       </c>
       <c r="K94" s="3">
         <v>-71100</v>
@@ -4227,22 +4227,22 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-69200</v>
+        <v>69200</v>
       </c>
       <c r="E96" s="3">
-        <v>-59400</v>
+        <v>61100</v>
       </c>
       <c r="F96" s="3">
-        <v>-94900</v>
+        <v>106000</v>
       </c>
       <c r="G96" s="3">
-        <v>-91800</v>
+        <v>99700</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-84000</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-158500</v>
+        <v>-158600</v>
       </c>
       <c r="E100" s="3">
-        <v>-160700</v>
+        <v>-165300</v>
       </c>
       <c r="F100" s="3">
-        <v>408600</v>
+        <v>456200</v>
       </c>
       <c r="G100" s="3">
-        <v>-77100</v>
+        <v>-83800</v>
       </c>
       <c r="H100" s="3">
-        <v>9700</v>
+        <v>9900</v>
       </c>
       <c r="I100" s="3">
-        <v>-76700</v>
+        <v>-79100</v>
       </c>
       <c r="J100" s="3">
-        <v>8600</v>
+        <v>9400</v>
       </c>
       <c r="K100" s="3">
         <v>3900</v>
@@ -4455,19 +4455,19 @@
         <v>-2100</v>
       </c>
       <c r="E101" s="3">
-        <v>23700</v>
+        <v>24400</v>
       </c>
       <c r="F101" s="3">
-        <v>-6600</v>
+        <v>-7400</v>
       </c>
       <c r="G101" s="3">
-        <v>-2500</v>
+        <v>-2700</v>
       </c>
       <c r="H101" s="3">
         <v>-1900</v>
       </c>
       <c r="I101" s="3">
-        <v>5500</v>
+        <v>5700</v>
       </c>
       <c r="J101" s="3">
         <v>-400</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>326000</v>
+        <v>326100</v>
       </c>
       <c r="E102" s="3">
-        <v>-213700</v>
+        <v>-219800</v>
       </c>
       <c r="F102" s="3">
-        <v>361200</v>
+        <v>403400</v>
       </c>
       <c r="G102" s="3">
-        <v>-31600</v>
+        <v>-34400</v>
       </c>
       <c r="H102" s="3">
-        <v>250500</v>
+        <v>255100</v>
       </c>
       <c r="I102" s="3">
-        <v>-97900</v>
+        <v>-101000</v>
       </c>
       <c r="J102" s="3">
-        <v>-337200</v>
+        <v>-367600</v>
       </c>
       <c r="K102" s="3">
         <v>150400</v>

--- a/AAII_Financials/Yearly/ATHM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ATHM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>ATHM</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>964400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1013100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1006300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1139200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1326300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1209400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1051700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>954400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>823200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>482200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>333900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>185100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>105100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>63000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>203200</v>
+      </c>
+      <c r="E9" s="3">
         <v>185700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>165000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>158800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>132400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>110600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>85500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>134300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>282200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>52900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>29800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>21800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>25600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>761200</v>
+      </c>
+      <c r="E10" s="3">
         <v>827500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>841400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>980400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1193900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1098700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>966100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>820100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>541000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>429300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>304100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>163200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>79500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>44000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,53 +886,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>180600</v>
+      </c>
+      <c r="E12" s="3">
         <v>190200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>205500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>220100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>209000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>185400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>165100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>135100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>78900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>38100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>24800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>12400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2400</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,9 +979,12 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,20 +1003,20 @@
       <c r="H14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="3">
         <v>1600</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1008,36 +1027,39 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E15" s="3">
         <v>34500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>44200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>48600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>26100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>17000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>14800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>13700</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>827000</v>
+      </c>
+      <c r="E17" s="3">
         <v>852700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>825500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>858800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>844100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>744700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>634500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>639100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>663900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>315200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>192400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>100600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>62300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>38000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>137500</v>
+      </c>
+      <c r="E18" s="3">
         <v>160400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>180900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>280500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>482200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>464700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>417100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>315300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>159300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>167000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>141600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>84400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>42800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>25000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1179,98 +1211,105 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>13200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>10600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>156000</v>
+      </c>
+      <c r="E21" s="3">
         <v>199000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>217900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>329100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>508100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>481900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>435500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>327400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>182100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>185500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>153800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>91400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>47100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>30500</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1295,8 +1334,8 @@
       <c r="J22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1305,107 +1344,116 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>231000</v>
+      </c>
+      <c r="E23" s="3">
         <v>281700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>255600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>342700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>542100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>531500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>471300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>347600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>172400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>177600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>147400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>86500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>43600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>25300</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E24" s="3">
         <v>10200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-9000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>40000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>71900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>54900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>41000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>39700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>30200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>17100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>13100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5600</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>222400</v>
+      </c>
+      <c r="E26" s="3">
         <v>271500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>264500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>337400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>502100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>459700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>416400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>306500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>167900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>137900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>117200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>69400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>30500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>19700</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>221900</v>
+      </c>
+      <c r="E27" s="3">
         <v>265100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>262000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>338200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>501700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>459600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>417400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>307600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>169600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>137900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>117200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>69400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>30500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>19700</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1626,11 +1686,14 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-600</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E32" s="3">
         <v>4100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-13200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-10600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>245500</v>
+      </c>
+      <c r="E33" s="3">
         <v>272900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>269000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>354000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>501700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>459600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>417400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>307600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>169600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>137900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>117200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>69400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>30500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>19100</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>245500</v>
+      </c>
+      <c r="E35" s="3">
         <v>272900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>269000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>354000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>501700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>459600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>417400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>307600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>169600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>137900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>117200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>69400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>30500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>19100</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,88 +2072,92 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>232000</v>
+      </c>
+      <c r="E41" s="3">
         <v>704600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>406200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>666900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>268200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>285600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>30800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>140100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>454800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>299600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>165100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>173200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>60300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>31100</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2962300</v>
+      </c>
+      <c r="E42" s="3">
         <v>2616400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2795300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2596800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1972600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1552100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1432100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1113100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>335800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>273600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>269100</v>
-      </c>
-      <c r="N42" s="3">
-        <v>300</v>
       </c>
       <c r="O42" s="3">
         <v>300</v>
@@ -2076,54 +2165,60 @@
       <c r="P42" s="3">
         <v>300</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>300</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>194900</v>
+      </c>
+      <c r="E43" s="3">
         <v>215800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>292200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>356600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>524200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>477300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>418600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>299200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>342900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>156800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>119800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>71200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>46900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>30200</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2148,15 +2243,15 @@
       <c r="J44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L44" s="3">
         <v>13200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>15500</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>17</v>
       </c>
@@ -2166,132 +2261,141 @@
       <c r="P44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="3">
         <v>41700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>43000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>37500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>47800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>34500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>29200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>24200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>111900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>53800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>44200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4100</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3447500</v>
+      </c>
+      <c r="E46" s="3">
         <v>3599700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3541300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3671800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2812900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2349400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1910700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1576600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1026300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>799400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>570000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>288900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>112800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>65700</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>46500</v>
+      </c>
+      <c r="E47" s="3">
         <v>63200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>60800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>11100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>10800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>119100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>108500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>22700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>18700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>17300</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>17</v>
       </c>
@@ -2301,99 +2405,108 @@
       <c r="P47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E48" s="3">
         <v>56400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>53700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>81100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>94900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>52100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>24700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>37200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>557600</v>
+      </c>
+      <c r="E49" s="3">
         <v>584400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>611900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>676800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>691100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>220000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>224400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>239000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>423600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>214100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>241700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>235700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>222900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>227400</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E52" s="3">
         <v>3200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>21600</v>
-      </c>
-      <c r="L52" s="3">
-        <v>3000</v>
       </c>
       <c r="M52" s="3">
         <v>3000</v>
       </c>
       <c r="N52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O52" s="3">
         <v>900</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4140500</v>
+      </c>
+      <c r="E54" s="3">
         <v>4348600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4308400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4470500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3634900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2751100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2290900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1889600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1296900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1048200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>826400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>534400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>341400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>297100</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,8 +2784,9 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2681,183 +2811,195 @@
       <c r="J57" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L57" s="3">
         <v>2300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3300</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
       <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3">
         <v>700</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>15100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>15100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>17200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7600</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>4300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>24400</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>400</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>218900</v>
+      </c>
+      <c r="E59" s="3">
         <v>317800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>231600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>332100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>284100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>243000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>278300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>369400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>503700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>272600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>169200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>119700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>48300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>29000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>620600</v>
+      </c>
+      <c r="E60" s="3">
         <v>715800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>588500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>627500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>641100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>569600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>605500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>597700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>351300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>300200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>169200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>120100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>48300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>29600</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E61" s="3">
         <v>12600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>13900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3300</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2879,9 +3021,12 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2894,39 +3039,42 @@
       <c r="F62" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H62" s="3">
         <v>2200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>68600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>72700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>83400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>77700</v>
-      </c>
-      <c r="O62" s="3">
-        <v>69600</v>
       </c>
       <c r="P62" s="3">
         <v>69600</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>69600</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>687900</v>
+      </c>
+      <c r="E66" s="3">
         <v>798600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>670900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>722800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>753900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>653500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>675300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>670000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>418600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>372900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>252500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>197800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>117900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>99300</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="3">
         <v>2341200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2348300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2331500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2062600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1536500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1090200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>711200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>444800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>277500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>157000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>38700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>60600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>37000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3281500</v>
+      </c>
+      <c r="E76" s="3">
         <v>3374500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3463600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3561500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2699800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2101000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1619000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1222100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>878200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>675300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>573900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>336500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>223500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>197800</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>245500</v>
+      </c>
+      <c r="E81" s="3">
         <v>272900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>269000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>354000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>501700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>459600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>417400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>307600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>169600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>137900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>117200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>69400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>30500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>19100</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" s="3">
         <v>38900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>50000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>54700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>40900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>32900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>12600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5200</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E89" s="3">
         <v>345700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>371900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>554700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>509400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>415000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>452400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>378600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>217400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>203500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>160300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>90300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>40100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>21300</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-16900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-34400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-40400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-29300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-16500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12400</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-6700</v>
       </c>
       <c r="N91" s="3">
         <v>-6700</v>
       </c>
       <c r="O91" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="P91" s="3">
         <v>-4000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E94" s="3">
         <v>141100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-450800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-600200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-457300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-167800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-480000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-755200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-71100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-56700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-275500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,26 +4453,27 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>69200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>61100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>106000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>99700</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -4257,17 +4490,20 @@
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-33600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-6400</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E100" s="3">
         <v>-158600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-165300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>456200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-83800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>9900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-79100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>9400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>101400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>25800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>24400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-7400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>5700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>326100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-219800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>403400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-34400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>255100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-101000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-367600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>150400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>152900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>109200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>29700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5700</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ATHM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ATHM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>ATHM</t>
   </si>
@@ -777,7 +777,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>203200</v>
+        <v>191500</v>
       </c>
       <c r="E9" s="3">
         <v>185700</v>
@@ -825,7 +825,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>761200</v>
+        <v>772900</v>
       </c>
       <c r="E10" s="3">
         <v>827500</v>
@@ -1037,7 +1037,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>33500</v>
+        <v>27100</v>
       </c>
       <c r="E15" s="3">
         <v>34500</v>
@@ -1266,7 +1266,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>156000</v>
+        <v>149700</v>
       </c>
       <c r="E21" s="3">
         <v>199000</v>
@@ -1845,10 +1845,10 @@
         <v>245500</v>
       </c>
       <c r="E33" s="3">
-        <v>272900</v>
+        <v>286800</v>
       </c>
       <c r="F33" s="3">
-        <v>269000</v>
+        <v>282000</v>
       </c>
       <c r="G33" s="3">
         <v>354000</v>
@@ -1941,10 +1941,10 @@
         <v>245500</v>
       </c>
       <c r="E35" s="3">
-        <v>272900</v>
+        <v>286800</v>
       </c>
       <c r="F35" s="3">
-        <v>269000</v>
+        <v>282000</v>
       </c>
       <c r="G35" s="3">
         <v>354000</v>
@@ -2175,7 +2175,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>194900</v>
+        <v>201100</v>
       </c>
       <c r="E43" s="3">
         <v>215800</v>
@@ -2270,14 +2270,14 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>17</v>
+      <c r="D45" s="3">
+        <v>1800</v>
       </c>
       <c r="E45" s="3">
-        <v>41700</v>
+        <v>2000</v>
       </c>
       <c r="F45" s="3">
-        <v>43000</v>
+        <v>6300</v>
       </c>
       <c r="G45" s="3">
         <v>37500</v>
@@ -2415,7 +2415,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>28000</v>
+        <v>41500</v>
       </c>
       <c r="E48" s="3">
         <v>56400</v>
@@ -2607,7 +2607,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>18700</v>
+        <v>5200</v>
       </c>
       <c r="E52" s="3">
         <v>3200</v>
@@ -2839,7 +2839,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>10100</v>
       </c>
       <c r="E58" s="3">
         <v>15100</v>
@@ -2887,7 +2887,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>218900</v>
+        <v>250900</v>
       </c>
       <c r="E59" s="3">
         <v>317800</v>
@@ -3482,8 +3482,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>17</v>
+      <c r="D72" s="3">
+        <v>2293600</v>
       </c>
       <c r="E72" s="3">
         <v>2341200</v>
@@ -3827,10 +3827,10 @@
         <v>245500</v>
       </c>
       <c r="E81" s="3">
-        <v>272900</v>
+        <v>286800</v>
       </c>
       <c r="F81" s="3">
-        <v>269000</v>
+        <v>282000</v>
       </c>
       <c r="G81" s="3">
         <v>354000</v>
@@ -3891,8 +3891,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>17</v>
+      <c r="D83" s="3">
+        <v>31500</v>
       </c>
       <c r="E83" s="3">
         <v>38900</v>
@@ -4179,8 +4179,8 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>17</v>
+      <c r="D89" s="3">
+        <v>188100</v>
       </c>
       <c r="E89" s="3">
         <v>345700</v>
@@ -4247,8 +4247,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>17</v>
+      <c r="D91" s="3">
+        <v>-19200</v>
       </c>
       <c r="E91" s="3">
         <v>-11100</v>
@@ -4391,8 +4391,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>17</v>
+      <c r="D94" s="3">
+        <v>-418100</v>
       </c>
       <c r="E94" s="3">
         <v>141100</v>
@@ -4460,7 +4460,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>202900</v>
       </c>
       <c r="E96" s="3">
         <v>69200</v>
@@ -4651,8 +4651,8 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>17</v>
+      <c r="D100" s="3">
+        <v>-233100</v>
       </c>
       <c r="E100" s="3">
         <v>-158600</v>
@@ -4699,8 +4699,8 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>17</v>
+      <c r="D101" s="3">
+        <v>5400</v>
       </c>
       <c r="E101" s="3">
         <v>-2100</v>
@@ -4748,7 +4748,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-457700</v>
       </c>
       <c r="E102" s="3">
         <v>326100</v>

--- a/AAII_Financials/Yearly/ATHM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ATHM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>ATHM</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>922500</v>
+      </c>
+      <c r="E8" s="3">
         <v>964400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1013100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1006300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1139200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1326300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1209400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1051700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>954400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>823200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>482200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>333900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>185100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>105100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>63000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>245400</v>
+      </c>
+      <c r="E9" s="3">
         <v>191500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>185700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>165000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>158800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>132400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>110600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>85500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>134300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>282200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>52900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>29800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>21800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>25600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>677100</v>
+      </c>
+      <c r="E10" s="3">
         <v>772900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>827500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>841400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>980400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1193900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1098700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>966100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>820100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>541000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>429300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>304100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>163200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>79500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>44000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,56 +899,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>152100</v>
+      </c>
+      <c r="E12" s="3">
         <v>180600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>190200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>205500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>220100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>209000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>185400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>165100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>135100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>78900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>38100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>12400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2400</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -982,9 +998,12 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,20 +1025,20 @@
       <c r="I14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" s="3">
         <v>1600</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>17</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1030,39 +1049,42 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E15" s="3">
         <v>27100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>34500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>44200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>48600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>26100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>17000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>13700</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>812500</v>
+      </c>
+      <c r="E17" s="3">
         <v>827000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>852700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>825500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>858800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>844100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>744700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>634500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>639100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>663900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>315200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>192400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>100600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>62300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>38000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E18" s="3">
         <v>137500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>160400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>180900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>280500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>482200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>464700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>417100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>315300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>159300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>167000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>141600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>84400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>42800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>25000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1212,104 +1244,111 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E20" s="3">
         <v>14900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>7200</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>13200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>10600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>151100</v>
+      </c>
+      <c r="E21" s="3">
         <v>149700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>199000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>217900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>329100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>508100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>481900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>435500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>327400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>182100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>185500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>153800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>91400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>47100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>30500</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1337,8 +1376,8 @@
       <c r="K22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1347,113 +1386,122 @@
         <v>0</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>219000</v>
+      </c>
+      <c r="E23" s="3">
         <v>231000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>281700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>255600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>342700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>542100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>531500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>471300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>347600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>172400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>177600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>147400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>86500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>43600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>25300</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E24" s="3">
         <v>8600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-9000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>40000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>71900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>54900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>41000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>39700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>30200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>17100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>13100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5600</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>198700</v>
+      </c>
+      <c r="E26" s="3">
         <v>222400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>271500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>264500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>337400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>502100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>459700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>416400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>306500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>167900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>137900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>117200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>69400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>30500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>19700</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E27" s="3">
         <v>221900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>265100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>262000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>338200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>501700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>459600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>417400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>307600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>169600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>137900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>117200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>69400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>30500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19700</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1689,11 +1749,14 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-600</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-14900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-7200</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-13200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-10600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>245500</v>
+        <v>198000</v>
       </c>
       <c r="E33" s="3">
-        <v>286800</v>
+        <v>221900</v>
       </c>
       <c r="F33" s="3">
-        <v>282000</v>
+        <v>265100</v>
       </c>
       <c r="G33" s="3">
-        <v>354000</v>
+        <v>262000</v>
       </c>
       <c r="H33" s="3">
+        <v>338200</v>
+      </c>
+      <c r="I33" s="3">
         <v>501700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>459600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>417400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>307600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>169600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>137900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>117200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>69400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>30500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>19100</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>245500</v>
+        <v>198000</v>
       </c>
       <c r="E35" s="3">
-        <v>286800</v>
+        <v>221900</v>
       </c>
       <c r="F35" s="3">
-        <v>282000</v>
+        <v>265100</v>
       </c>
       <c r="G35" s="3">
-        <v>354000</v>
+        <v>262000</v>
       </c>
       <c r="H35" s="3">
+        <v>338200</v>
+      </c>
+      <c r="I35" s="3">
         <v>501700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>459600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>417400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>307600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>169600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>137900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>117200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>69400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>30500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>19100</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,94 +2158,98 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>311000</v>
+      </c>
+      <c r="E41" s="3">
         <v>232000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>704600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>406200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>666900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>268200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>285600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>30800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>140100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>454800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>299600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>165100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>173200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>60300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>31100</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2439600</v>
+      </c>
+      <c r="E42" s="3">
         <v>2962300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2616400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2795300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2596800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1972600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1552100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1432100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1113100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>335800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>273600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>269100</v>
-      </c>
-      <c r="O42" s="3">
-        <v>300</v>
       </c>
       <c r="P42" s="3">
         <v>300</v>
@@ -2168,57 +2257,63 @@
       <c r="Q42" s="3">
         <v>300</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>300</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>228900</v>
+      </c>
+      <c r="E43" s="3">
         <v>201100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>215800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>292200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>356600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>524200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>477300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>418600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>299200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>342900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>156800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>119800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>71200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>46900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>30200</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2246,15 +2341,15 @@
       <c r="K44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M44" s="3">
         <v>13200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>15500</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>17</v>
       </c>
@@ -2264,141 +2359,150 @@
       <c r="Q44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1800</v>
+        <v>8900</v>
       </c>
       <c r="E45" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F45" s="3">
         <v>2000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>37500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>47800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>34500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>29200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>24200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>111900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>53800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>44200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4100</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3029200</v>
+      </c>
+      <c r="E46" s="3">
         <v>3447500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3599700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3541300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3671800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2812900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2349400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1910700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1576600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1026300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>799400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>570000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>288900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>112800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>65700</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>367000</v>
+      </c>
+      <c r="E47" s="3">
         <v>46500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>63200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>60800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>11100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>10800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>119100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>108500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>22700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>18700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>17300</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>17</v>
       </c>
@@ -2408,105 +2512,114 @@
       <c r="Q47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E48" s="3">
         <v>41500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>56400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>53700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>81100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>94900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>52100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>24700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>37200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>571200</v>
+      </c>
+      <c r="E49" s="3">
         <v>557600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>584400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>611900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>676800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>691100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>220000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>224400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>239000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>423600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>214100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>241700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>235700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>222900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>227400</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E52" s="3">
         <v>5200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>21600</v>
-      </c>
-      <c r="M52" s="3">
-        <v>3000</v>
       </c>
       <c r="N52" s="3">
         <v>3000</v>
       </c>
       <c r="O52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P52" s="3">
         <v>900</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4047300</v>
+      </c>
+      <c r="E54" s="3">
         <v>4140500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4348600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4308400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4470500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3634900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2751100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2290900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1889600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1296900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1048200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>826400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>534400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>341400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>297100</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,8 +2914,9 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2814,195 +2944,207 @@
       <c r="K57" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M57" s="3">
         <v>2300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3300</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
       <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
       <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3">
         <v>700</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E58" s="3">
         <v>10100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>15100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>15100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>17200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7600</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>4300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>24400</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>400</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>208900</v>
+      </c>
+      <c r="E59" s="3">
         <v>250900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>317800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>231600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>332100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>284100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>243000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>278300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>369400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>503700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>272600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>169200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>119700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>48300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>29000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>505200</v>
+      </c>
+      <c r="E60" s="3">
         <v>620600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>715800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>588500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>627500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>641100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>569600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>605500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>597700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>351300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>300200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>169200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>120100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>48300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>29600</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E61" s="3">
         <v>3200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3300</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -3024,9 +3166,12 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3042,39 +3187,42 @@
       <c r="G62" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I62" s="3">
         <v>2200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>68600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>72700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>83400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>77700</v>
-      </c>
-      <c r="P62" s="3">
-        <v>69600</v>
       </c>
       <c r="Q62" s="3">
         <v>69600</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>69600</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>573800</v>
+      </c>
+      <c r="E66" s="3">
         <v>687900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>798600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>670900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>722800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>753900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>653500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>675300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>670000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>418600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>372900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>252500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>197800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>117900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>99300</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2380000</v>
+      </c>
+      <c r="E72" s="3">
         <v>2293600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2341200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2348300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2331500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2062600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1536500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1090200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>711200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>444800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>277500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>157000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>38700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>60600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>37000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3294300</v>
+      </c>
+      <c r="E76" s="3">
         <v>3281500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3374500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3463600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3561500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2699800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2101000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1619000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1222100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>878200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>675300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>573900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>336500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>223500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>197800</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>245500</v>
+        <v>198000</v>
       </c>
       <c r="E81" s="3">
-        <v>286800</v>
+        <v>221900</v>
       </c>
       <c r="F81" s="3">
-        <v>282000</v>
+        <v>265100</v>
       </c>
       <c r="G81" s="3">
-        <v>354000</v>
+        <v>262000</v>
       </c>
       <c r="H81" s="3">
+        <v>338200</v>
+      </c>
+      <c r="I81" s="3">
         <v>501700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>459600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>417400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>307600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>169600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>137900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>117200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>69400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>30500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>19100</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E83" s="3">
         <v>31500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>38900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>50000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>54700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>40900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>32900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5200</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>127200</v>
+      </c>
+      <c r="E89" s="3">
         <v>188100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>345700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>371900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>554700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>509400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>415000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>452400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>378600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>217400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>203500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>160300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>90300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>40100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>21300</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-19200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-16900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-34400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-40400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-29300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-16500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12400</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-6700</v>
       </c>
       <c r="O91" s="3">
         <v>-6700</v>
       </c>
       <c r="P91" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4600</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>307700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-418100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>141100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-450800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-600200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-457300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-167800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-480000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-755200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-71100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-56700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-275500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1800</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,29 +4686,30 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>211800</v>
+      </c>
+      <c r="E96" s="3">
         <v>202900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>69200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>61100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>106000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>99700</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -4493,17 +4726,20 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-33600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-362200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-233100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-158600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-165300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>456200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-83800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>9900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-79100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>9400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>4200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>101400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>25800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-13700</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E101" s="3">
         <v>5400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>24400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-7400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>5700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>66900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-457700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>326100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-219800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>403400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-34400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>255100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-101000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-367600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>150400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>152900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>109200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>29700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5700</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
